--- a/cirt_data.xlsx
+++ b/cirt_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://o365coloradoedu-my.sharepoint.com/personal/daad2295_colorado_edu/Documents/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ce1ebde9cded71ae/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="162" documentId="13_ncr:1_{C6350078-5CFC-4B20-8D31-D68148B331D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B0C2A44B-F12B-4A10-B25E-2DE39C4B0491}"/>
+  <xr:revisionPtr revIDLastSave="166" documentId="13_ncr:1_{C6350078-5CFC-4B20-8D31-D68148B331D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A0E237A-3892-4FBD-ABF0-177C512E6849}"/>
   <bookViews>
-    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{969D6A76-162A-4286-A653-6BBA36AECB0D}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{969D6A76-162A-4286-A653-6BBA36AECB0D}"/>
   </bookViews>
   <sheets>
     <sheet name="courses" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">courses!$A$1:$O$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">topics!$A$1:$P$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">topics!$A$1:$Q$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8199" uniqueCount="2616">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8333" uniqueCount="2616">
   <si>
     <t>Effective Communication: Writing</t>
   </si>
@@ -29464,7 +29464,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B785887B-576B-4D81-AE70-D107EA8277F5}">
-  <dimension ref="A1:Q134"/>
+  <dimension ref="A1:R134"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="3" width="9.81640625" customWidth="1"/>
@@ -29472,11 +29472,11 @@
     <col min="5" max="5" width="17.54296875" customWidth="1"/>
     <col min="6" max="6" width="47.7265625" customWidth="1"/>
     <col min="7" max="7" width="9.81640625" style="4" customWidth="1"/>
-    <col min="8" max="16" width="9.81640625" customWidth="1"/>
-    <col min="17" max="29" width="14.81640625" customWidth="1"/>
+    <col min="8" max="17" width="9.81640625" customWidth="1"/>
+    <col min="18" max="30" width="14.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>305</v>
       </c>
@@ -29502,31 +29502,34 @@
         <v>304</v>
       </c>
       <c r="I1" t="s">
+        <v>2592</v>
+      </c>
+      <c r="J1" t="s">
         <v>312</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>313</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>314</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>315</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>316</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>317</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>318</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>231</v>
       </c>
@@ -29552,17 +29555,17 @@
         <v>48</v>
       </c>
       <c r="I2" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J2" t="s">
         <v>6</v>
       </c>
-      <c r="J2" t="s">
-        <v>49</v>
-      </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" t="s">
+        <v>49</v>
+      </c>
+      <c r="L2" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L2" t="s">
-        <v>2434</v>
-      </c>
       <c r="M2" t="s">
         <v>2434</v>
       </c>
@@ -29573,11 +29576,14 @@
         <v>2434</v>
       </c>
       <c r="P2" t="s">
-        <v>2557</v>
-      </c>
-      <c r="Q2" s="2"/>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
+        <v>2434</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>2557</v>
+      </c>
+      <c r="R2" s="2"/>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>233</v>
       </c>
@@ -29603,17 +29609,17 @@
         <v>48</v>
       </c>
       <c r="I3" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J3" t="s">
         <v>235</v>
       </c>
-      <c r="J3" t="s">
-        <v>49</v>
-      </c>
-      <c r="K3" s="4" t="s">
+      <c r="K3" t="s">
+        <v>49</v>
+      </c>
+      <c r="L3" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L3" t="s">
-        <v>2434</v>
-      </c>
       <c r="M3" t="s">
         <v>2434</v>
       </c>
@@ -29621,14 +29627,17 @@
         <v>2434</v>
       </c>
       <c r="O3" t="s">
+        <v>2434</v>
+      </c>
+      <c r="P3" t="s">
         <v>2462</v>
       </c>
-      <c r="P3" t="s">
-        <v>2557</v>
-      </c>
-      <c r="Q3" s="2"/>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="Q3" t="s">
+        <v>2557</v>
+      </c>
+      <c r="R3" s="2"/>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>260</v>
       </c>
@@ -29654,17 +29663,17 @@
         <v>48</v>
       </c>
       <c r="I4" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J4" t="s">
         <v>262</v>
       </c>
-      <c r="J4" t="s">
-        <v>49</v>
-      </c>
-      <c r="K4" s="4" t="s">
+      <c r="K4" t="s">
+        <v>49</v>
+      </c>
+      <c r="L4" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L4" t="s">
-        <v>2434</v>
-      </c>
       <c r="M4" t="s">
         <v>2434</v>
       </c>
@@ -29675,11 +29684,14 @@
         <v>2434</v>
       </c>
       <c r="P4" t="s">
-        <v>2557</v>
-      </c>
-      <c r="Q4" s="2"/>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
+        <v>2434</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>2557</v>
+      </c>
+      <c r="R4" s="2"/>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>263</v>
       </c>
@@ -29705,31 +29717,34 @@
         <v>48</v>
       </c>
       <c r="I5" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J5" t="s">
         <v>265</v>
       </c>
-      <c r="J5" t="s">
-        <v>49</v>
-      </c>
-      <c r="K5" s="4" t="s">
+      <c r="K5" t="s">
+        <v>49</v>
+      </c>
+      <c r="L5" s="4" t="s">
         <v>2426</v>
       </c>
-      <c r="L5" t="s">
+      <c r="M5" t="s">
         <v>2435</v>
       </c>
-      <c r="M5" t="s">
-        <v>2446</v>
-      </c>
       <c r="N5" t="s">
+        <v>2446</v>
+      </c>
+      <c r="O5" t="s">
         <v>2426</v>
       </c>
-      <c r="O5" t="s">
-        <v>2446</v>
-      </c>
       <c r="P5" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
+        <v>2446</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>164</v>
       </c>
@@ -29755,17 +29770,17 @@
         <v>48</v>
       </c>
       <c r="I6" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J6" t="s">
         <v>6</v>
       </c>
-      <c r="J6" t="s">
-        <v>49</v>
-      </c>
-      <c r="K6" s="4" t="s">
+      <c r="K6" t="s">
+        <v>49</v>
+      </c>
+      <c r="L6" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L6" t="s">
-        <v>2434</v>
-      </c>
       <c r="M6" t="s">
         <v>2434</v>
       </c>
@@ -29773,13 +29788,16 @@
         <v>2434</v>
       </c>
       <c r="O6" t="s">
+        <v>2434</v>
+      </c>
+      <c r="P6" t="s">
         <v>2461</v>
       </c>
-      <c r="P6" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="Q6" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>166</v>
       </c>
@@ -29805,31 +29823,34 @@
         <v>48</v>
       </c>
       <c r="I7" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J7" t="s">
         <v>168</v>
       </c>
-      <c r="J7" t="s">
-        <v>49</v>
-      </c>
-      <c r="K7" s="4" t="s">
+      <c r="K7" t="s">
+        <v>49</v>
+      </c>
+      <c r="L7" s="4" t="s">
         <v>2423</v>
       </c>
-      <c r="L7" t="s">
+      <c r="M7" t="s">
         <v>2439</v>
       </c>
-      <c r="M7" t="s">
+      <c r="N7" t="s">
         <v>2445</v>
       </c>
-      <c r="N7" s="5" t="s">
+      <c r="O7" s="5" t="s">
         <v>2445</v>
       </c>
-      <c r="O7" t="s">
+      <c r="P7" t="s">
         <v>2459</v>
       </c>
-      <c r="P7" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="Q7" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>182</v>
       </c>
@@ -29855,17 +29876,17 @@
         <v>48</v>
       </c>
       <c r="I8" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J8" t="s">
         <v>177</v>
       </c>
-      <c r="J8" t="s">
-        <v>49</v>
-      </c>
-      <c r="K8" s="4" t="s">
+      <c r="K8" t="s">
+        <v>49</v>
+      </c>
+      <c r="L8" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L8" t="s">
-        <v>2434</v>
-      </c>
       <c r="M8" t="s">
         <v>2434</v>
       </c>
@@ -29876,10 +29897,13 @@
         <v>2434</v>
       </c>
       <c r="P8" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
+        <v>2434</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>238</v>
       </c>
@@ -29905,31 +29929,34 @@
         <v>2579</v>
       </c>
       <c r="I9" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J9" t="s">
         <v>6</v>
       </c>
-      <c r="J9" t="s">
-        <v>49</v>
-      </c>
-      <c r="K9" s="4" t="s">
+      <c r="K9" t="s">
+        <v>49</v>
+      </c>
+      <c r="L9" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L9" t="s">
-        <v>2434</v>
-      </c>
       <c r="M9" t="s">
+        <v>2434</v>
+      </c>
+      <c r="N9" t="s">
         <v>2452</v>
       </c>
-      <c r="N9" t="s">
-        <v>2434</v>
-      </c>
       <c r="O9" t="s">
         <v>2434</v>
       </c>
       <c r="P9" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
+        <v>2434</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>241</v>
       </c>
@@ -29955,31 +29982,34 @@
         <v>2579</v>
       </c>
       <c r="I10" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J10" t="s">
         <v>6</v>
       </c>
-      <c r="J10" t="s">
-        <v>49</v>
-      </c>
-      <c r="K10" s="4" t="s">
+      <c r="K10" t="s">
+        <v>49</v>
+      </c>
+      <c r="L10" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L10" t="s">
-        <v>2434</v>
-      </c>
       <c r="M10" t="s">
+        <v>2434</v>
+      </c>
+      <c r="N10" t="s">
         <v>2452</v>
       </c>
-      <c r="N10" t="s">
-        <v>2434</v>
-      </c>
       <c r="O10" t="s">
         <v>2434</v>
       </c>
       <c r="P10" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
+        <v>2434</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>247</v>
       </c>
@@ -30005,31 +30035,34 @@
         <v>2580</v>
       </c>
       <c r="I11" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J11" t="s">
         <v>6</v>
       </c>
-      <c r="J11" t="s">
-        <v>49</v>
-      </c>
-      <c r="K11" s="4" t="s">
+      <c r="K11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L11" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L11" t="s">
-        <v>2434</v>
-      </c>
       <c r="M11" t="s">
+        <v>2434</v>
+      </c>
+      <c r="N11" t="s">
         <v>2452</v>
       </c>
-      <c r="N11" t="s">
-        <v>2434</v>
-      </c>
       <c r="O11" t="s">
         <v>2434</v>
       </c>
       <c r="P11" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
+        <v>2434</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>255</v>
       </c>
@@ -30055,17 +30088,17 @@
         <v>278</v>
       </c>
       <c r="I12" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J12" t="s">
         <v>6</v>
       </c>
-      <c r="J12" t="s">
-        <v>49</v>
-      </c>
-      <c r="K12" s="4" t="s">
+      <c r="K12" t="s">
+        <v>49</v>
+      </c>
+      <c r="L12" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L12" t="s">
-        <v>2434</v>
-      </c>
       <c r="M12" t="s">
         <v>2434</v>
       </c>
@@ -30076,10 +30109,13 @@
         <v>2434</v>
       </c>
       <c r="P12" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
+        <v>2434</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>257</v>
       </c>
@@ -30105,17 +30141,17 @@
         <v>278</v>
       </c>
       <c r="I13" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J13" t="s">
         <v>6</v>
       </c>
-      <c r="J13" t="s">
-        <v>49</v>
-      </c>
-      <c r="K13" s="4" t="s">
+      <c r="K13" t="s">
+        <v>49</v>
+      </c>
+      <c r="L13" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L13" t="s">
-        <v>2434</v>
-      </c>
       <c r="M13" t="s">
         <v>2434</v>
       </c>
@@ -30126,10 +30162,13 @@
         <v>2434</v>
       </c>
       <c r="P13" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
+        <v>2434</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>175</v>
       </c>
@@ -30155,31 +30194,34 @@
         <v>278</v>
       </c>
       <c r="I14" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J14" t="s">
         <v>177</v>
       </c>
-      <c r="J14" t="s">
-        <v>49</v>
-      </c>
-      <c r="K14" s="4" t="s">
+      <c r="K14" t="s">
+        <v>49</v>
+      </c>
+      <c r="L14" s="4" t="s">
         <v>2429</v>
       </c>
-      <c r="L14" t="s">
+      <c r="M14" t="s">
         <v>2442</v>
       </c>
-      <c r="M14" t="s">
+      <c r="N14" t="s">
         <v>2450</v>
       </c>
-      <c r="N14" t="s">
-        <v>2434</v>
-      </c>
       <c r="O14" t="s">
         <v>2434</v>
       </c>
       <c r="P14" t="s">
+        <v>2434</v>
+      </c>
+      <c r="Q14" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>169</v>
       </c>
@@ -30205,17 +30247,17 @@
         <v>278</v>
       </c>
       <c r="I15" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J15" t="s">
         <v>6</v>
       </c>
-      <c r="J15" t="s">
-        <v>49</v>
-      </c>
-      <c r="K15" s="4" t="s">
+      <c r="K15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L15" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L15" t="s">
-        <v>2434</v>
-      </c>
       <c r="M15" t="s">
         <v>2434</v>
       </c>
@@ -30226,10 +30268,13 @@
         <v>2434</v>
       </c>
       <c r="P15" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
+        <v>2434</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>170</v>
       </c>
@@ -30255,17 +30300,17 @@
         <v>278</v>
       </c>
       <c r="I16" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J16" t="s">
         <v>171</v>
       </c>
-      <c r="J16" t="s">
-        <v>49</v>
-      </c>
-      <c r="K16" s="4" t="s">
+      <c r="K16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L16" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L16" t="s">
-        <v>2434</v>
-      </c>
       <c r="M16" t="s">
         <v>2434</v>
       </c>
@@ -30276,10 +30321,13 @@
         <v>2434</v>
       </c>
       <c r="P16" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2434</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>172</v>
       </c>
@@ -30305,17 +30353,17 @@
         <v>278</v>
       </c>
       <c r="I17" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J17" t="s">
         <v>174</v>
       </c>
-      <c r="J17" t="s">
-        <v>49</v>
-      </c>
-      <c r="K17" s="4" t="s">
+      <c r="K17" t="s">
+        <v>49</v>
+      </c>
+      <c r="L17" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L17" t="s">
-        <v>2434</v>
-      </c>
       <c r="M17" t="s">
         <v>2434</v>
       </c>
@@ -30326,10 +30374,13 @@
         <v>2434</v>
       </c>
       <c r="P17" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2434</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>220</v>
       </c>
@@ -30355,31 +30406,34 @@
         <v>271</v>
       </c>
       <c r="I18" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J18" t="s">
         <v>6</v>
       </c>
-      <c r="J18" t="s">
-        <v>49</v>
-      </c>
-      <c r="K18" s="4" t="s">
+      <c r="K18" t="s">
+        <v>49</v>
+      </c>
+      <c r="L18" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L18" t="s">
-        <v>2434</v>
-      </c>
       <c r="M18" t="s">
+        <v>2434</v>
+      </c>
+      <c r="N18" t="s">
         <v>2452</v>
       </c>
-      <c r="N18" t="s">
-        <v>2434</v>
-      </c>
       <c r="O18" t="s">
+        <v>2434</v>
+      </c>
+      <c r="P18" t="s">
         <v>2462</v>
       </c>
-      <c r="P18" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q18" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>240</v>
       </c>
@@ -30405,31 +30459,34 @@
         <v>271</v>
       </c>
       <c r="I19" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J19" t="s">
         <v>6</v>
       </c>
-      <c r="J19" t="s">
-        <v>49</v>
-      </c>
-      <c r="K19" s="4" t="s">
+      <c r="K19" t="s">
+        <v>49</v>
+      </c>
+      <c r="L19" s="4" t="s">
         <v>2431</v>
       </c>
-      <c r="L19" t="s">
+      <c r="M19" t="s">
         <v>2435</v>
       </c>
-      <c r="M19" t="s">
-        <v>2446</v>
-      </c>
       <c r="N19" t="s">
+        <v>2446</v>
+      </c>
+      <c r="O19" t="s">
         <v>2426</v>
       </c>
-      <c r="O19" t="s">
-        <v>2446</v>
-      </c>
       <c r="P19" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2446</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>159</v>
       </c>
@@ -30455,17 +30512,17 @@
         <v>271</v>
       </c>
       <c r="I20" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J20" t="s">
         <v>160</v>
       </c>
-      <c r="J20" t="s">
-        <v>49</v>
-      </c>
-      <c r="K20" s="4" t="s">
+      <c r="K20" t="s">
+        <v>49</v>
+      </c>
+      <c r="L20" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L20" t="s">
-        <v>2434</v>
-      </c>
       <c r="M20" t="s">
         <v>2434</v>
       </c>
@@ -30476,10 +30533,13 @@
         <v>2434</v>
       </c>
       <c r="P20" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2434</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>161</v>
       </c>
@@ -30505,17 +30565,17 @@
         <v>271</v>
       </c>
       <c r="I21" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J21" t="s">
         <v>6</v>
       </c>
-      <c r="J21" t="s">
-        <v>49</v>
-      </c>
-      <c r="K21" s="4" t="s">
+      <c r="K21" t="s">
+        <v>49</v>
+      </c>
+      <c r="L21" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L21" t="s">
-        <v>2434</v>
-      </c>
       <c r="M21" t="s">
         <v>2434</v>
       </c>
@@ -30526,10 +30586,13 @@
         <v>2434</v>
       </c>
       <c r="P21" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2434</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>163</v>
       </c>
@@ -30555,17 +30618,17 @@
         <v>271</v>
       </c>
       <c r="I22" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J22" t="s">
         <v>6</v>
       </c>
-      <c r="J22" t="s">
-        <v>49</v>
-      </c>
-      <c r="K22" s="4" t="s">
+      <c r="K22" t="s">
+        <v>49</v>
+      </c>
+      <c r="L22" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L22" t="s">
-        <v>2434</v>
-      </c>
       <c r="M22" t="s">
         <v>2434</v>
       </c>
@@ -30573,13 +30636,16 @@
         <v>2434</v>
       </c>
       <c r="O22" t="s">
+        <v>2434</v>
+      </c>
+      <c r="P22" t="s">
         <v>2461</v>
       </c>
-      <c r="P22" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q22" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>216</v>
       </c>
@@ -30605,31 +30671,34 @@
         <v>2581</v>
       </c>
       <c r="I23" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J23" t="s">
         <v>6</v>
       </c>
-      <c r="J23" t="s">
-        <v>49</v>
-      </c>
-      <c r="K23" s="4" t="s">
+      <c r="K23" t="s">
+        <v>49</v>
+      </c>
+      <c r="L23" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L23" t="s">
-        <v>2434</v>
-      </c>
       <c r="M23" t="s">
+        <v>2434</v>
+      </c>
+      <c r="N23" t="s">
         <v>2452</v>
       </c>
-      <c r="N23" t="s">
-        <v>2434</v>
-      </c>
       <c r="O23" t="s">
         <v>2434</v>
       </c>
       <c r="P23" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2434</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>248</v>
       </c>
@@ -30655,31 +30724,34 @@
         <v>2582</v>
       </c>
       <c r="I24" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J24" t="s">
         <v>6</v>
       </c>
-      <c r="J24" t="s">
-        <v>49</v>
-      </c>
-      <c r="K24" s="4" t="s">
+      <c r="K24" t="s">
+        <v>49</v>
+      </c>
+      <c r="L24" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L24" t="s">
-        <v>2434</v>
-      </c>
       <c r="M24" t="s">
+        <v>2434</v>
+      </c>
+      <c r="N24" t="s">
         <v>2452</v>
       </c>
-      <c r="N24" t="s">
-        <v>2434</v>
-      </c>
       <c r="O24" t="s">
         <v>2434</v>
       </c>
       <c r="P24" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2434</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>215</v>
       </c>
@@ -30705,31 +30777,34 @@
         <v>2583</v>
       </c>
       <c r="I25" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J25" t="s">
         <v>6</v>
       </c>
-      <c r="J25" t="s">
-        <v>49</v>
-      </c>
-      <c r="K25" s="4" t="s">
+      <c r="K25" t="s">
+        <v>49</v>
+      </c>
+      <c r="L25" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L25" t="s">
-        <v>2434</v>
-      </c>
       <c r="M25" t="s">
+        <v>2434</v>
+      </c>
+      <c r="N25" t="s">
         <v>2452</v>
       </c>
-      <c r="N25" t="s">
-        <v>2434</v>
-      </c>
       <c r="O25" t="s">
         <v>2434</v>
       </c>
       <c r="P25" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2434</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>204</v>
       </c>
@@ -30755,17 +30830,17 @@
         <v>2584</v>
       </c>
       <c r="I26" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J26" t="s">
         <v>177</v>
       </c>
-      <c r="J26" t="s">
-        <v>49</v>
-      </c>
-      <c r="K26" s="4" t="s">
+      <c r="K26" t="s">
+        <v>49</v>
+      </c>
+      <c r="L26" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L26" t="s">
-        <v>2434</v>
-      </c>
       <c r="M26" t="s">
         <v>2434</v>
       </c>
@@ -30776,10 +30851,13 @@
         <v>2434</v>
       </c>
       <c r="P26" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2434</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>245</v>
       </c>
@@ -30805,31 +30883,34 @@
         <v>2585</v>
       </c>
       <c r="I27" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J27" t="s">
         <v>6</v>
       </c>
-      <c r="J27" t="s">
-        <v>49</v>
-      </c>
-      <c r="K27" s="4" t="s">
+      <c r="K27" t="s">
+        <v>49</v>
+      </c>
+      <c r="L27" s="4" t="s">
         <v>2431</v>
       </c>
-      <c r="L27" t="s">
+      <c r="M27" t="s">
         <v>2435</v>
       </c>
-      <c r="M27" t="s">
-        <v>2446</v>
-      </c>
       <c r="N27" t="s">
+        <v>2446</v>
+      </c>
+      <c r="O27" t="s">
         <v>2426</v>
       </c>
-      <c r="O27" t="s">
-        <v>2446</v>
-      </c>
       <c r="P27" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2446</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>236</v>
       </c>
@@ -30855,31 +30936,34 @@
         <v>2586</v>
       </c>
       <c r="I28" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J28" t="s">
         <v>185</v>
       </c>
-      <c r="J28" t="s">
-        <v>49</v>
-      </c>
-      <c r="K28" s="4" t="s">
+      <c r="K28" t="s">
+        <v>49</v>
+      </c>
+      <c r="L28" s="4" t="s">
         <v>2431</v>
       </c>
-      <c r="L28" t="s">
+      <c r="M28" t="s">
         <v>2435</v>
       </c>
-      <c r="M28" t="s">
-        <v>2446</v>
-      </c>
       <c r="N28" t="s">
+        <v>2446</v>
+      </c>
+      <c r="O28" t="s">
         <v>2426</v>
       </c>
-      <c r="O28" t="s">
-        <v>2446</v>
-      </c>
       <c r="P28" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2446</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>266</v>
       </c>
@@ -30905,31 +30989,34 @@
         <v>2586</v>
       </c>
       <c r="I29" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J29" t="s">
         <v>187</v>
       </c>
-      <c r="J29" t="s">
-        <v>49</v>
-      </c>
-      <c r="K29" s="4" t="s">
+      <c r="K29" t="s">
+        <v>49</v>
+      </c>
+      <c r="L29" s="4" t="s">
         <v>2424</v>
       </c>
-      <c r="L29" t="s">
+      <c r="M29" t="s">
         <v>2435</v>
       </c>
-      <c r="M29" t="s">
-        <v>2446</v>
-      </c>
       <c r="N29" t="s">
+        <v>2446</v>
+      </c>
+      <c r="O29" t="s">
         <v>2426</v>
       </c>
-      <c r="O29" t="s">
-        <v>2446</v>
-      </c>
       <c r="P29" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2446</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>183</v>
       </c>
@@ -30955,31 +31042,34 @@
         <v>2586</v>
       </c>
       <c r="I30" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J30" t="s">
         <v>185</v>
       </c>
-      <c r="J30" t="s">
-        <v>49</v>
-      </c>
-      <c r="K30" s="4" t="s">
+      <c r="K30" t="s">
+        <v>49</v>
+      </c>
+      <c r="L30" s="4" t="s">
         <v>2431</v>
       </c>
-      <c r="L30" t="s">
+      <c r="M30" t="s">
         <v>2435</v>
       </c>
-      <c r="M30" t="s">
-        <v>2446</v>
-      </c>
       <c r="N30" t="s">
+        <v>2446</v>
+      </c>
+      <c r="O30" t="s">
         <v>2426</v>
       </c>
-      <c r="O30" t="s">
-        <v>2446</v>
-      </c>
       <c r="P30" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2446</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>243</v>
       </c>
@@ -31005,31 +31095,34 @@
         <v>2587</v>
       </c>
       <c r="I31" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J31" t="s">
         <v>6</v>
       </c>
-      <c r="J31" t="s">
-        <v>49</v>
-      </c>
-      <c r="K31" s="4" t="s">
+      <c r="K31" t="s">
+        <v>49</v>
+      </c>
+      <c r="L31" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L31" t="s">
-        <v>2434</v>
-      </c>
       <c r="M31" t="s">
+        <v>2434</v>
+      </c>
+      <c r="N31" t="s">
         <v>2452</v>
       </c>
-      <c r="N31" t="s">
-        <v>2434</v>
-      </c>
       <c r="O31" t="s">
         <v>2434</v>
       </c>
       <c r="P31" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2434</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>258</v>
       </c>
@@ -31055,17 +31148,17 @@
         <v>2588</v>
       </c>
       <c r="I32" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J32" t="s">
         <v>6</v>
       </c>
-      <c r="J32" t="s">
-        <v>49</v>
-      </c>
-      <c r="K32" s="4" t="s">
+      <c r="K32" t="s">
+        <v>49</v>
+      </c>
+      <c r="L32" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L32" t="s">
-        <v>2434</v>
-      </c>
       <c r="M32" t="s">
         <v>2434</v>
       </c>
@@ -31076,10 +31169,13 @@
         <v>2434</v>
       </c>
       <c r="P32" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2434</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>211</v>
       </c>
@@ -31105,17 +31201,17 @@
         <v>2589</v>
       </c>
       <c r="I33" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J33" t="s">
         <v>6</v>
       </c>
-      <c r="J33" t="s">
-        <v>49</v>
-      </c>
-      <c r="K33" s="4" t="s">
+      <c r="K33" t="s">
+        <v>49</v>
+      </c>
+      <c r="L33" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L33" t="s">
-        <v>2434</v>
-      </c>
       <c r="M33" t="s">
         <v>2434</v>
       </c>
@@ -31126,10 +31222,13 @@
         <v>2434</v>
       </c>
       <c r="P33" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2434</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>222</v>
       </c>
@@ -31155,31 +31254,34 @@
         <v>108</v>
       </c>
       <c r="I34" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J34" t="s">
         <v>6</v>
       </c>
-      <c r="J34" t="s">
-        <v>49</v>
-      </c>
-      <c r="K34" s="4" t="s">
+      <c r="K34" t="s">
+        <v>49</v>
+      </c>
+      <c r="L34" s="4" t="s">
         <v>2432</v>
       </c>
-      <c r="L34" t="s">
+      <c r="M34" t="s">
         <v>2444</v>
       </c>
-      <c r="M34" t="s">
+      <c r="N34" t="s">
         <v>2453</v>
       </c>
-      <c r="N34" t="s">
-        <v>2434</v>
-      </c>
       <c r="O34" t="s">
+        <v>2434</v>
+      </c>
+      <c r="P34" t="s">
         <v>2463</v>
       </c>
-      <c r="P34" t="s">
+      <c r="Q34" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>221</v>
       </c>
@@ -31205,31 +31307,34 @@
         <v>2590</v>
       </c>
       <c r="I35" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J35" t="s">
         <v>6</v>
       </c>
-      <c r="J35" t="s">
-        <v>49</v>
-      </c>
-      <c r="K35" s="4" t="s">
+      <c r="K35" t="s">
+        <v>49</v>
+      </c>
+      <c r="L35" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L35" t="s">
-        <v>2434</v>
-      </c>
       <c r="M35" t="s">
+        <v>2434</v>
+      </c>
+      <c r="N35" t="s">
         <v>2452</v>
       </c>
-      <c r="N35" t="s">
-        <v>2434</v>
-      </c>
       <c r="O35" t="s">
+        <v>2434</v>
+      </c>
+      <c r="P35" t="s">
         <v>2462</v>
       </c>
-      <c r="P35" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q35" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>219</v>
       </c>
@@ -31255,31 +31360,34 @@
         <v>2578</v>
       </c>
       <c r="I36" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J36" t="s">
         <v>6</v>
       </c>
-      <c r="J36" t="s">
-        <v>49</v>
-      </c>
-      <c r="K36" s="4" t="s">
+      <c r="K36" t="s">
+        <v>49</v>
+      </c>
+      <c r="L36" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L36" t="s">
-        <v>2434</v>
-      </c>
       <c r="M36" t="s">
+        <v>2434</v>
+      </c>
+      <c r="N36" t="s">
         <v>2452</v>
       </c>
-      <c r="N36" t="s">
-        <v>2434</v>
-      </c>
       <c r="O36" t="s">
         <v>2434</v>
       </c>
       <c r="P36" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2434</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>217</v>
       </c>
@@ -31305,31 +31413,34 @@
         <v>271</v>
       </c>
       <c r="I37" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J37" t="s">
         <v>6</v>
       </c>
-      <c r="J37" t="s">
-        <v>49</v>
-      </c>
-      <c r="K37" s="4" t="s">
+      <c r="K37" t="s">
+        <v>49</v>
+      </c>
+      <c r="L37" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L37" t="s">
-        <v>2434</v>
-      </c>
       <c r="M37" t="s">
+        <v>2434</v>
+      </c>
+      <c r="N37" t="s">
         <v>2452</v>
       </c>
-      <c r="N37" t="s">
-        <v>2434</v>
-      </c>
       <c r="O37" t="s">
+        <v>2434</v>
+      </c>
+      <c r="P37" t="s">
         <v>2461</v>
       </c>
-      <c r="P37" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q37" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>267</v>
       </c>
@@ -31355,17 +31466,17 @@
         <v>2578</v>
       </c>
       <c r="I38" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J38" t="s">
         <v>6</v>
       </c>
-      <c r="J38" t="s">
-        <v>49</v>
-      </c>
-      <c r="K38" s="4" t="s">
+      <c r="K38" t="s">
+        <v>49</v>
+      </c>
+      <c r="L38" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L38" t="s">
-        <v>2434</v>
-      </c>
       <c r="M38" t="s">
         <v>2434</v>
       </c>
@@ -31376,10 +31487,13 @@
         <v>2434</v>
       </c>
       <c r="P38" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2434</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>209</v>
       </c>
@@ -31405,31 +31519,34 @@
         <v>48</v>
       </c>
       <c r="I39" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J39" t="s">
         <v>210</v>
       </c>
-      <c r="J39" t="s">
-        <v>49</v>
-      </c>
-      <c r="K39" s="4" t="s">
+      <c r="K39" t="s">
+        <v>49</v>
+      </c>
+      <c r="L39" s="4" t="s">
         <v>2431</v>
       </c>
-      <c r="L39" t="s">
+      <c r="M39" t="s">
         <v>2435</v>
       </c>
-      <c r="M39" t="s">
-        <v>2446</v>
-      </c>
       <c r="N39" t="s">
+        <v>2446</v>
+      </c>
+      <c r="O39" t="s">
         <v>2426</v>
       </c>
-      <c r="O39" t="s">
-        <v>2446</v>
-      </c>
       <c r="P39" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2446</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>186</v>
       </c>
@@ -31455,31 +31572,34 @@
         <v>2579</v>
       </c>
       <c r="I40" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J40" t="s">
         <v>187</v>
       </c>
-      <c r="J40" t="s">
-        <v>49</v>
-      </c>
-      <c r="K40" s="4" t="s">
+      <c r="K40" t="s">
+        <v>49</v>
+      </c>
+      <c r="L40" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L40" t="s">
-        <v>2434</v>
-      </c>
       <c r="M40" t="s">
+        <v>2434</v>
+      </c>
+      <c r="N40" t="s">
         <v>2452</v>
       </c>
-      <c r="N40" t="s">
-        <v>2434</v>
-      </c>
       <c r="O40" t="s">
         <v>2434</v>
       </c>
       <c r="P40" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2434</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>188</v>
       </c>
@@ -31505,17 +31625,17 @@
         <v>2579</v>
       </c>
       <c r="I41" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J41" t="s">
         <v>160</v>
       </c>
-      <c r="J41" t="s">
-        <v>49</v>
-      </c>
-      <c r="K41" s="4" t="s">
+      <c r="K41" t="s">
+        <v>49</v>
+      </c>
+      <c r="L41" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L41" t="s">
-        <v>2434</v>
-      </c>
       <c r="M41" t="s">
         <v>2434</v>
       </c>
@@ -31523,13 +31643,16 @@
         <v>2434</v>
       </c>
       <c r="O41" t="s">
+        <v>2434</v>
+      </c>
+      <c r="P41" t="s">
         <v>2461</v>
       </c>
-      <c r="P41" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q41" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>189</v>
       </c>
@@ -31555,17 +31678,17 @@
         <v>2579</v>
       </c>
       <c r="I42" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J42" t="s">
         <v>191</v>
       </c>
-      <c r="J42" t="s">
-        <v>49</v>
-      </c>
-      <c r="K42" s="4" t="s">
+      <c r="K42" t="s">
+        <v>49</v>
+      </c>
+      <c r="L42" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L42" t="s">
-        <v>2434</v>
-      </c>
       <c r="M42" t="s">
         <v>2434</v>
       </c>
@@ -31576,10 +31699,13 @@
         <v>2434</v>
       </c>
       <c r="P42" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2434</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>192</v>
       </c>
@@ -31605,17 +31731,17 @@
         <v>2579</v>
       </c>
       <c r="I43" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J43" t="s">
         <v>6</v>
       </c>
-      <c r="J43" t="s">
-        <v>49</v>
-      </c>
-      <c r="K43" s="4" t="s">
+      <c r="K43" t="s">
+        <v>49</v>
+      </c>
+      <c r="L43" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L43" t="s">
-        <v>2434</v>
-      </c>
       <c r="M43" t="s">
         <v>2434</v>
       </c>
@@ -31626,10 +31752,13 @@
         <v>2434</v>
       </c>
       <c r="P43" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2434</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>193</v>
       </c>
@@ -31655,17 +31784,17 @@
         <v>2579</v>
       </c>
       <c r="I44" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J44" t="s">
         <v>6</v>
       </c>
-      <c r="J44" t="s">
-        <v>49</v>
-      </c>
-      <c r="K44" s="4" t="s">
+      <c r="K44" t="s">
+        <v>49</v>
+      </c>
+      <c r="L44" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L44" t="s">
-        <v>2434</v>
-      </c>
       <c r="M44" t="s">
         <v>2434</v>
       </c>
@@ -31676,10 +31805,13 @@
         <v>2434</v>
       </c>
       <c r="P44" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2434</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>194</v>
       </c>
@@ -31705,17 +31837,17 @@
         <v>2576</v>
       </c>
       <c r="I45" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J45" t="s">
         <v>6</v>
       </c>
-      <c r="J45" t="s">
-        <v>49</v>
-      </c>
-      <c r="K45" s="4" t="s">
+      <c r="K45" t="s">
+        <v>49</v>
+      </c>
+      <c r="L45" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L45" t="s">
-        <v>2434</v>
-      </c>
       <c r="M45" t="s">
         <v>2434</v>
       </c>
@@ -31726,10 +31858,13 @@
         <v>2434</v>
       </c>
       <c r="P45" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2434</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>195</v>
       </c>
@@ -31755,17 +31890,17 @@
         <v>2579</v>
       </c>
       <c r="I46" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J46" t="s">
         <v>6</v>
       </c>
-      <c r="J46" t="s">
-        <v>49</v>
-      </c>
-      <c r="K46" s="4" t="s">
+      <c r="K46" t="s">
+        <v>49</v>
+      </c>
+      <c r="L46" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L46" t="s">
-        <v>2434</v>
-      </c>
       <c r="M46" t="s">
         <v>2434</v>
       </c>
@@ -31776,10 +31911,13 @@
         <v>2434</v>
       </c>
       <c r="P46" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2434</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>197</v>
       </c>
@@ -31805,17 +31943,17 @@
         <v>2579</v>
       </c>
       <c r="I47" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J47" t="s">
         <v>6</v>
       </c>
-      <c r="J47" t="s">
-        <v>49</v>
-      </c>
-      <c r="K47" s="4" t="s">
+      <c r="K47" t="s">
+        <v>49</v>
+      </c>
+      <c r="L47" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L47" t="s">
-        <v>2434</v>
-      </c>
       <c r="M47" t="s">
         <v>2434</v>
       </c>
@@ -31826,10 +31964,13 @@
         <v>2434</v>
       </c>
       <c r="P47" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2434</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>198</v>
       </c>
@@ -31855,17 +31996,17 @@
         <v>2579</v>
       </c>
       <c r="I48" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J48" t="s">
         <v>6</v>
       </c>
-      <c r="J48" t="s">
-        <v>49</v>
-      </c>
-      <c r="K48" s="4" t="s">
+      <c r="K48" t="s">
+        <v>49</v>
+      </c>
+      <c r="L48" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L48" t="s">
-        <v>2434</v>
-      </c>
       <c r="M48" t="s">
         <v>2434</v>
       </c>
@@ -31876,10 +32017,13 @@
         <v>2434</v>
       </c>
       <c r="P48" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2434</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>200</v>
       </c>
@@ -31905,17 +32049,17 @@
         <v>2579</v>
       </c>
       <c r="I49" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J49" t="s">
         <v>6</v>
       </c>
-      <c r="J49" t="s">
-        <v>49</v>
-      </c>
-      <c r="K49" s="4" t="s">
+      <c r="K49" t="s">
+        <v>49</v>
+      </c>
+      <c r="L49" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L49" t="s">
-        <v>2434</v>
-      </c>
       <c r="M49" t="s">
         <v>2434</v>
       </c>
@@ -31926,10 +32070,13 @@
         <v>2434</v>
       </c>
       <c r="P49" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2434</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>202</v>
       </c>
@@ -31955,17 +32102,17 @@
         <v>2579</v>
       </c>
       <c r="I50" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J50" t="s">
         <v>6</v>
       </c>
-      <c r="J50" t="s">
-        <v>49</v>
-      </c>
-      <c r="K50" s="4" t="s">
+      <c r="K50" t="s">
+        <v>49</v>
+      </c>
+      <c r="L50" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L50" t="s">
-        <v>2434</v>
-      </c>
       <c r="M50" t="s">
         <v>2434</v>
       </c>
@@ -31976,10 +32123,13 @@
         <v>2434</v>
       </c>
       <c r="P50" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2434</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>207</v>
       </c>
@@ -32005,17 +32155,17 @@
         <v>2591</v>
       </c>
       <c r="I51" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J51" t="s">
         <v>177</v>
       </c>
-      <c r="J51" t="s">
-        <v>49</v>
-      </c>
-      <c r="K51" s="4" t="s">
+      <c r="K51" t="s">
+        <v>49</v>
+      </c>
+      <c r="L51" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L51" t="s">
-        <v>2434</v>
-      </c>
       <c r="M51" t="s">
         <v>2434</v>
       </c>
@@ -32026,10 +32176,13 @@
         <v>2434</v>
       </c>
       <c r="P51" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2434</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>206</v>
       </c>
@@ -32055,17 +32208,17 @@
         <v>271</v>
       </c>
       <c r="I52" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J52" t="s">
         <v>177</v>
       </c>
-      <c r="J52" t="s">
-        <v>49</v>
-      </c>
-      <c r="K52" s="4" t="s">
+      <c r="K52" t="s">
+        <v>49</v>
+      </c>
+      <c r="L52" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L52" t="s">
-        <v>2434</v>
-      </c>
       <c r="M52" t="s">
         <v>2434</v>
       </c>
@@ -32076,10 +32229,13 @@
         <v>2434</v>
       </c>
       <c r="P52" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2434</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>157</v>
       </c>
@@ -32105,31 +32261,34 @@
         <v>158</v>
       </c>
       <c r="I53" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J53" t="s">
         <v>103</v>
       </c>
-      <c r="J53" t="s">
-        <v>49</v>
-      </c>
-      <c r="K53" s="4" t="s">
+      <c r="K53" t="s">
+        <v>49</v>
+      </c>
+      <c r="L53" s="4" t="s">
         <v>2428</v>
       </c>
-      <c r="L53" t="s">
+      <c r="M53" t="s">
         <v>2440</v>
       </c>
-      <c r="M53" t="s">
-        <v>2446</v>
-      </c>
       <c r="N53" t="s">
+        <v>2446</v>
+      </c>
+      <c r="O53" t="s">
         <v>2426</v>
       </c>
-      <c r="O53" t="s">
-        <v>2446</v>
-      </c>
       <c r="P53" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2446</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>118</v>
       </c>
@@ -32155,31 +32314,34 @@
         <v>120</v>
       </c>
       <c r="I54" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J54" t="s">
         <v>6</v>
       </c>
-      <c r="J54" t="s">
-        <v>49</v>
-      </c>
-      <c r="K54" s="4" t="s">
+      <c r="K54" t="s">
+        <v>49</v>
+      </c>
+      <c r="L54" s="4" t="s">
         <v>2424</v>
       </c>
-      <c r="L54" t="s">
+      <c r="M54" t="s">
         <v>2436</v>
       </c>
-      <c r="M54" t="s">
+      <c r="N54" t="s">
         <v>2448</v>
       </c>
-      <c r="N54" t="s">
+      <c r="O54" t="s">
         <v>2426</v>
       </c>
-      <c r="O54" t="s">
-        <v>2446</v>
-      </c>
       <c r="P54" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2446</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>121</v>
       </c>
@@ -32205,31 +32367,34 @@
         <v>123</v>
       </c>
       <c r="I55" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J55" t="s">
         <v>6</v>
       </c>
-      <c r="J55" t="s">
-        <v>49</v>
-      </c>
-      <c r="K55" s="4" t="s">
+      <c r="K55" t="s">
+        <v>49</v>
+      </c>
+      <c r="L55" s="4" t="s">
         <v>2424</v>
       </c>
-      <c r="L55" t="s">
+      <c r="M55" t="s">
         <v>2436</v>
       </c>
-      <c r="M55" t="s">
+      <c r="N55" t="s">
         <v>2448</v>
       </c>
-      <c r="N55" t="s">
+      <c r="O55" t="s">
         <v>2426</v>
       </c>
-      <c r="O55" t="s">
-        <v>2446</v>
-      </c>
       <c r="P55" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2446</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>146</v>
       </c>
@@ -32255,31 +32420,34 @@
         <v>147</v>
       </c>
       <c r="I56" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J56" t="s">
         <v>6</v>
       </c>
-      <c r="J56" t="s">
-        <v>49</v>
-      </c>
-      <c r="K56" s="4" t="s">
+      <c r="K56" t="s">
+        <v>49</v>
+      </c>
+      <c r="L56" s="4" t="s">
         <v>2427</v>
       </c>
-      <c r="L56" t="s">
+      <c r="M56" t="s">
         <v>2441</v>
       </c>
-      <c r="M56" t="s">
+      <c r="N56" t="s">
         <v>2449</v>
       </c>
-      <c r="N56" t="s">
+      <c r="O56" t="s">
         <v>2458</v>
       </c>
-      <c r="O56" t="s">
+      <c r="P56" t="s">
         <v>2460</v>
       </c>
-      <c r="P56" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q56" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>54</v>
       </c>
@@ -32305,31 +32473,34 @@
         <v>55</v>
       </c>
       <c r="I57" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J57" t="s">
         <v>6</v>
       </c>
-      <c r="J57" t="s">
-        <v>49</v>
-      </c>
-      <c r="K57" s="4" t="s">
+      <c r="K57" t="s">
+        <v>49</v>
+      </c>
+      <c r="L57" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L57" t="s">
-        <v>2434</v>
-      </c>
       <c r="M57" t="s">
         <v>2434</v>
       </c>
       <c r="N57" t="s">
+        <v>2434</v>
+      </c>
+      <c r="O57" t="s">
         <v>2456</v>
       </c>
-      <c r="O57" t="s">
-        <v>2434</v>
-      </c>
       <c r="P57" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2434</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>143</v>
       </c>
@@ -32355,17 +32526,17 @@
         <v>145</v>
       </c>
       <c r="I58" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J58" t="s">
         <v>6</v>
       </c>
-      <c r="J58" t="s">
-        <v>49</v>
-      </c>
-      <c r="K58" s="4" t="s">
+      <c r="K58" t="s">
+        <v>49</v>
+      </c>
+      <c r="L58" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L58" t="s">
-        <v>2434</v>
-      </c>
       <c r="M58" t="s">
         <v>2434</v>
       </c>
@@ -32376,10 +32547,13 @@
         <v>2434</v>
       </c>
       <c r="P58" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2434</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>75</v>
       </c>
@@ -32405,31 +32579,34 @@
         <v>48</v>
       </c>
       <c r="I59" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J59" t="s">
         <v>77</v>
       </c>
-      <c r="J59" t="s">
-        <v>49</v>
-      </c>
-      <c r="K59" s="4" t="s">
+      <c r="K59" t="s">
+        <v>49</v>
+      </c>
+      <c r="L59" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L59" t="s">
-        <v>2434</v>
-      </c>
       <c r="M59" t="s">
         <v>2434</v>
       </c>
       <c r="N59" t="s">
+        <v>2434</v>
+      </c>
+      <c r="O59" t="s">
         <v>2456</v>
       </c>
-      <c r="O59" t="s">
-        <v>2434</v>
-      </c>
       <c r="P59" t="s">
+        <v>2434</v>
+      </c>
+      <c r="Q59" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>50</v>
       </c>
@@ -32455,31 +32632,34 @@
         <v>48</v>
       </c>
       <c r="I60" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J60" t="s">
         <v>6</v>
       </c>
-      <c r="J60" t="s">
-        <v>49</v>
-      </c>
-      <c r="K60" s="4" t="s">
+      <c r="K60" t="s">
+        <v>49</v>
+      </c>
+      <c r="L60" s="4" t="s">
         <v>2423</v>
       </c>
-      <c r="L60" t="s">
+      <c r="M60" t="s">
         <v>2439</v>
       </c>
-      <c r="M60" t="s">
+      <c r="N60" t="s">
         <v>2445</v>
       </c>
-      <c r="N60" s="5" t="s">
+      <c r="O60" s="5" t="s">
         <v>2445</v>
       </c>
-      <c r="O60" t="s">
+      <c r="P60" t="s">
         <v>2459</v>
       </c>
-      <c r="P60" t="s">
+      <c r="Q60" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>303</v>
       </c>
@@ -32505,17 +32685,17 @@
         <v>48</v>
       </c>
       <c r="I61" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J61" t="s">
         <v>301</v>
       </c>
-      <c r="J61" t="s">
-        <v>49</v>
-      </c>
-      <c r="K61" s="4" t="s">
+      <c r="K61" t="s">
+        <v>49</v>
+      </c>
+      <c r="L61" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L61" t="s">
-        <v>2434</v>
-      </c>
       <c r="M61" t="s">
         <v>2434</v>
       </c>
@@ -32526,10 +32706,13 @@
         <v>2434</v>
       </c>
       <c r="P61" t="s">
+        <v>2434</v>
+      </c>
+      <c r="Q61" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>292</v>
       </c>
@@ -32555,31 +32738,34 @@
         <v>48</v>
       </c>
       <c r="I62" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J62" t="s">
         <v>6</v>
       </c>
-      <c r="J62" t="s">
-        <v>49</v>
-      </c>
-      <c r="K62" s="4" t="s">
+      <c r="K62" t="s">
+        <v>49</v>
+      </c>
+      <c r="L62" s="4" t="s">
         <v>2424</v>
       </c>
-      <c r="L62" t="s">
+      <c r="M62" t="s">
         <v>2435</v>
       </c>
-      <c r="M62" t="s">
-        <v>2446</v>
-      </c>
       <c r="N62" t="s">
+        <v>2446</v>
+      </c>
+      <c r="O62" t="s">
         <v>2426</v>
       </c>
-      <c r="O62" t="s">
-        <v>2446</v>
-      </c>
       <c r="P62" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2446</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>58</v>
       </c>
@@ -32605,31 +32791,34 @@
         <v>48</v>
       </c>
       <c r="I63" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J63" t="s">
         <v>6</v>
       </c>
-      <c r="J63" t="s">
-        <v>49</v>
-      </c>
-      <c r="K63" s="4" t="s">
+      <c r="K63" t="s">
+        <v>49</v>
+      </c>
+      <c r="L63" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L63" t="s">
-        <v>2434</v>
-      </c>
       <c r="M63" t="s">
         <v>2434</v>
       </c>
       <c r="N63" t="s">
+        <v>2434</v>
+      </c>
+      <c r="O63" t="s">
         <v>2456</v>
       </c>
-      <c r="O63" s="6" t="s">
-        <v>2434</v>
-      </c>
-      <c r="P63" t="s">
+      <c r="P63" s="6" t="s">
+        <v>2434</v>
+      </c>
+      <c r="Q63" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>99</v>
       </c>
@@ -32655,31 +32844,34 @@
         <v>48</v>
       </c>
       <c r="I64" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J64" t="s">
         <v>6</v>
       </c>
-      <c r="J64" t="s">
-        <v>49</v>
-      </c>
-      <c r="K64" s="4" t="s">
+      <c r="K64" t="s">
+        <v>49</v>
+      </c>
+      <c r="L64" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L64" t="s">
-        <v>2434</v>
-      </c>
       <c r="M64" t="s">
         <v>2434</v>
       </c>
       <c r="N64" t="s">
+        <v>2434</v>
+      </c>
+      <c r="O64" t="s">
         <v>2456</v>
       </c>
-      <c r="O64" t="s">
-        <v>2434</v>
-      </c>
       <c r="P64" t="s">
+        <v>2434</v>
+      </c>
+      <c r="Q64" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>109</v>
       </c>
@@ -32705,31 +32897,34 @@
         <v>48</v>
       </c>
       <c r="I65" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J65" t="s">
         <v>6</v>
       </c>
-      <c r="J65" t="s">
-        <v>49</v>
-      </c>
-      <c r="K65" s="4" t="s">
+      <c r="K65" t="s">
+        <v>49</v>
+      </c>
+      <c r="L65" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L65" t="s">
-        <v>2434</v>
-      </c>
       <c r="M65" t="s">
         <v>2434</v>
       </c>
       <c r="N65" t="s">
+        <v>2434</v>
+      </c>
+      <c r="O65" t="s">
         <v>2456</v>
       </c>
-      <c r="O65" t="s">
-        <v>2434</v>
-      </c>
       <c r="P65" t="s">
+        <v>2434</v>
+      </c>
+      <c r="Q65" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>124</v>
       </c>
@@ -32755,31 +32950,34 @@
         <v>48</v>
       </c>
       <c r="I66" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J66" t="s">
         <v>6</v>
       </c>
-      <c r="J66" t="s">
-        <v>49</v>
-      </c>
-      <c r="K66" s="4" t="s">
+      <c r="K66" t="s">
+        <v>49</v>
+      </c>
+      <c r="L66" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L66" t="s">
-        <v>2434</v>
-      </c>
       <c r="M66" t="s">
         <v>2434</v>
       </c>
       <c r="N66" t="s">
+        <v>2434</v>
+      </c>
+      <c r="O66" t="s">
         <v>2456</v>
       </c>
-      <c r="O66" t="s">
-        <v>2434</v>
-      </c>
       <c r="P66" t="s">
+        <v>2434</v>
+      </c>
+      <c r="Q66" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>47</v>
       </c>
@@ -32805,31 +33003,34 @@
         <v>48</v>
       </c>
       <c r="I67" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J67" t="s">
         <v>6</v>
       </c>
-      <c r="J67" t="s">
-        <v>49</v>
-      </c>
-      <c r="K67" s="4" t="s">
+      <c r="K67" t="s">
+        <v>49</v>
+      </c>
+      <c r="L67" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L67" t="s">
-        <v>2434</v>
-      </c>
       <c r="M67" t="s">
         <v>2434</v>
       </c>
       <c r="N67" t="s">
+        <v>2434</v>
+      </c>
+      <c r="O67" t="s">
         <v>2456</v>
       </c>
-      <c r="O67" t="s">
-        <v>2434</v>
-      </c>
       <c r="P67" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2434</v>
+      </c>
+      <c r="Q67" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="68" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>63</v>
       </c>
@@ -32855,31 +33056,34 @@
         <v>48</v>
       </c>
       <c r="I68" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J68" t="s">
         <v>6</v>
       </c>
-      <c r="J68" t="s">
-        <v>49</v>
-      </c>
-      <c r="K68" s="4" t="s">
+      <c r="K68" t="s">
+        <v>49</v>
+      </c>
+      <c r="L68" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L68" t="s">
-        <v>2434</v>
-      </c>
       <c r="M68" t="s">
         <v>2434</v>
       </c>
       <c r="N68" t="s">
+        <v>2434</v>
+      </c>
+      <c r="O68" t="s">
         <v>2456</v>
       </c>
-      <c r="O68" t="s">
-        <v>2434</v>
-      </c>
       <c r="P68" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2434</v>
+      </c>
+      <c r="Q68" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="69" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>69</v>
       </c>
@@ -32905,31 +33109,34 @@
         <v>48</v>
       </c>
       <c r="I69" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J69" t="s">
         <v>6</v>
       </c>
-      <c r="J69" t="s">
-        <v>49</v>
-      </c>
-      <c r="K69" s="4" t="s">
+      <c r="K69" t="s">
+        <v>49</v>
+      </c>
+      <c r="L69" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L69" t="s">
-        <v>2434</v>
-      </c>
       <c r="M69" t="s">
         <v>2434</v>
       </c>
       <c r="N69" t="s">
+        <v>2434</v>
+      </c>
+      <c r="O69" t="s">
         <v>2456</v>
       </c>
-      <c r="O69" t="s">
-        <v>2434</v>
-      </c>
       <c r="P69" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2434</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="70" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>70</v>
       </c>
@@ -32955,31 +33162,34 @@
         <v>48</v>
       </c>
       <c r="I70" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J70" t="s">
         <v>6</v>
       </c>
-      <c r="J70" t="s">
-        <v>49</v>
-      </c>
-      <c r="K70" s="4" t="s">
+      <c r="K70" t="s">
+        <v>49</v>
+      </c>
+      <c r="L70" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L70" t="s">
-        <v>2434</v>
-      </c>
       <c r="M70" t="s">
         <v>2434</v>
       </c>
       <c r="N70" t="s">
+        <v>2434</v>
+      </c>
+      <c r="O70" t="s">
         <v>2456</v>
       </c>
-      <c r="O70" t="s">
-        <v>2434</v>
-      </c>
       <c r="P70" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2434</v>
+      </c>
+      <c r="Q70" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="71" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>71</v>
       </c>
@@ -33005,31 +33215,34 @@
         <v>48</v>
       </c>
       <c r="I71" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J71" t="s">
         <v>6</v>
       </c>
-      <c r="J71" t="s">
-        <v>49</v>
-      </c>
-      <c r="K71" s="4" t="s">
+      <c r="K71" t="s">
+        <v>49</v>
+      </c>
+      <c r="L71" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L71" t="s">
-        <v>2434</v>
-      </c>
       <c r="M71" t="s">
         <v>2434</v>
       </c>
       <c r="N71" t="s">
+        <v>2434</v>
+      </c>
+      <c r="O71" t="s">
         <v>2456</v>
       </c>
-      <c r="O71" t="s">
-        <v>2434</v>
-      </c>
       <c r="P71" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2434</v>
+      </c>
+      <c r="Q71" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="72" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>73</v>
       </c>
@@ -33055,31 +33268,34 @@
         <v>48</v>
       </c>
       <c r="I72" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J72" t="s">
         <v>6</v>
       </c>
-      <c r="J72" t="s">
-        <v>49</v>
-      </c>
-      <c r="K72" s="4" t="s">
+      <c r="K72" t="s">
+        <v>49</v>
+      </c>
+      <c r="L72" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L72" t="s">
-        <v>2434</v>
-      </c>
       <c r="M72" t="s">
         <v>2434</v>
       </c>
       <c r="N72" t="s">
+        <v>2434</v>
+      </c>
+      <c r="O72" t="s">
         <v>2456</v>
       </c>
-      <c r="O72" t="s">
-        <v>2434</v>
-      </c>
       <c r="P72" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2434</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="73" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>79</v>
       </c>
@@ -33105,31 +33321,34 @@
         <v>48</v>
       </c>
       <c r="I73" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J73" t="s">
         <v>77</v>
       </c>
-      <c r="J73" t="s">
-        <v>49</v>
-      </c>
-      <c r="K73" s="4" t="s">
+      <c r="K73" t="s">
+        <v>49</v>
+      </c>
+      <c r="L73" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L73" t="s">
-        <v>2434</v>
-      </c>
       <c r="M73" t="s">
         <v>2434</v>
       </c>
       <c r="N73" t="s">
+        <v>2434</v>
+      </c>
+      <c r="O73" t="s">
         <v>2456</v>
       </c>
-      <c r="O73" t="s">
-        <v>2434</v>
-      </c>
       <c r="P73" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2434</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="74" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>81</v>
       </c>
@@ -33155,31 +33374,34 @@
         <v>48</v>
       </c>
       <c r="I74" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J74" t="s">
         <v>83</v>
       </c>
-      <c r="J74" t="s">
-        <v>49</v>
-      </c>
-      <c r="K74" s="4" t="s">
+      <c r="K74" t="s">
+        <v>49</v>
+      </c>
+      <c r="L74" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L74" t="s">
-        <v>2434</v>
-      </c>
       <c r="M74" t="s">
         <v>2434</v>
       </c>
       <c r="N74" t="s">
+        <v>2434</v>
+      </c>
+      <c r="O74" t="s">
         <v>2456</v>
       </c>
-      <c r="O74" t="s">
-        <v>2434</v>
-      </c>
       <c r="P74" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2434</v>
+      </c>
+      <c r="Q74" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="75" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>84</v>
       </c>
@@ -33205,31 +33427,34 @@
         <v>48</v>
       </c>
       <c r="I75" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J75" t="s">
         <v>6</v>
       </c>
-      <c r="J75" t="s">
-        <v>49</v>
-      </c>
-      <c r="K75" s="4" t="s">
+      <c r="K75" t="s">
+        <v>49</v>
+      </c>
+      <c r="L75" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L75" t="s">
-        <v>2434</v>
-      </c>
       <c r="M75" t="s">
         <v>2434</v>
       </c>
       <c r="N75" t="s">
+        <v>2434</v>
+      </c>
+      <c r="O75" t="s">
         <v>2456</v>
       </c>
-      <c r="O75" t="s">
-        <v>2434</v>
-      </c>
       <c r="P75" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2434</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="76" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>96</v>
       </c>
@@ -33255,31 +33480,34 @@
         <v>48</v>
       </c>
       <c r="I76" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J76" t="s">
         <v>98</v>
       </c>
-      <c r="J76" t="s">
-        <v>49</v>
-      </c>
-      <c r="K76" s="4" t="s">
+      <c r="K76" t="s">
+        <v>49</v>
+      </c>
+      <c r="L76" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L76" t="s">
-        <v>2434</v>
-      </c>
       <c r="M76" t="s">
         <v>2434</v>
       </c>
       <c r="N76" t="s">
+        <v>2434</v>
+      </c>
+      <c r="O76" t="s">
         <v>2456</v>
       </c>
-      <c r="O76" t="s">
-        <v>2434</v>
-      </c>
       <c r="P76" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2434</v>
+      </c>
+      <c r="Q76" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="77" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>104</v>
       </c>
@@ -33305,31 +33533,34 @@
         <v>48</v>
       </c>
       <c r="I77" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J77" t="s">
         <v>6</v>
       </c>
-      <c r="J77" t="s">
-        <v>49</v>
-      </c>
-      <c r="K77" s="4" t="s">
+      <c r="K77" t="s">
+        <v>49</v>
+      </c>
+      <c r="L77" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L77" t="s">
-        <v>2434</v>
-      </c>
       <c r="M77" t="s">
         <v>2434</v>
       </c>
       <c r="N77" t="s">
+        <v>2434</v>
+      </c>
+      <c r="O77" t="s">
         <v>2456</v>
       </c>
-      <c r="O77" t="s">
-        <v>2434</v>
-      </c>
       <c r="P77" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2434</v>
+      </c>
+      <c r="Q77" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="78" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>111</v>
       </c>
@@ -33355,31 +33586,34 @@
         <v>48</v>
       </c>
       <c r="I78" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J78" t="s">
         <v>6</v>
       </c>
-      <c r="J78" t="s">
-        <v>49</v>
-      </c>
-      <c r="K78" s="4" t="s">
+      <c r="K78" t="s">
+        <v>49</v>
+      </c>
+      <c r="L78" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L78" t="s">
-        <v>2434</v>
-      </c>
       <c r="M78" t="s">
         <v>2434</v>
       </c>
       <c r="N78" t="s">
+        <v>2434</v>
+      </c>
+      <c r="O78" t="s">
         <v>2456</v>
       </c>
-      <c r="O78" t="s">
-        <v>2434</v>
-      </c>
       <c r="P78" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2434</v>
+      </c>
+      <c r="Q78" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="79" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>132</v>
       </c>
@@ -33405,17 +33639,17 @@
         <v>48</v>
       </c>
       <c r="I79" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J79" t="s">
         <v>6</v>
       </c>
-      <c r="J79" t="s">
-        <v>49</v>
-      </c>
-      <c r="K79" s="4" t="s">
+      <c r="K79" t="s">
+        <v>49</v>
+      </c>
+      <c r="L79" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L79" t="s">
-        <v>2434</v>
-      </c>
       <c r="M79" t="s">
         <v>2434</v>
       </c>
@@ -33426,10 +33660,13 @@
         <v>2434</v>
       </c>
       <c r="P79" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2434</v>
+      </c>
+      <c r="Q79" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="80" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>155</v>
       </c>
@@ -33455,17 +33692,17 @@
         <v>48</v>
       </c>
       <c r="I80" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J80" t="s">
         <v>6</v>
       </c>
-      <c r="J80" t="s">
-        <v>49</v>
-      </c>
-      <c r="K80" s="4" t="s">
+      <c r="K80" t="s">
+        <v>49</v>
+      </c>
+      <c r="L80" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L80" t="s">
-        <v>2434</v>
-      </c>
       <c r="M80" t="s">
         <v>2434</v>
       </c>
@@ -33476,10 +33713,13 @@
         <v>2434</v>
       </c>
       <c r="P80" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2434</v>
+      </c>
+      <c r="Q80" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="81" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>286</v>
       </c>
@@ -33505,31 +33745,34 @@
         <v>288</v>
       </c>
       <c r="I81" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J81" t="s">
         <v>6</v>
       </c>
-      <c r="J81" t="s">
-        <v>49</v>
-      </c>
-      <c r="K81" s="4" t="s">
+      <c r="K81" t="s">
+        <v>49</v>
+      </c>
+      <c r="L81" s="4" t="s">
         <v>2424</v>
       </c>
-      <c r="L81" t="s">
+      <c r="M81" t="s">
         <v>2435</v>
       </c>
-      <c r="M81" t="s">
-        <v>2446</v>
-      </c>
       <c r="N81" t="s">
+        <v>2446</v>
+      </c>
+      <c r="O81" t="s">
         <v>2426</v>
       </c>
-      <c r="O81" t="s">
-        <v>2446</v>
-      </c>
       <c r="P81" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2446</v>
+      </c>
+      <c r="Q81" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="82" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>289</v>
       </c>
@@ -33555,31 +33798,34 @@
         <v>291</v>
       </c>
       <c r="I82" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J82" t="s">
         <v>6</v>
       </c>
-      <c r="J82" t="s">
-        <v>49</v>
-      </c>
-      <c r="K82" s="4" t="s">
+      <c r="K82" t="s">
+        <v>49</v>
+      </c>
+      <c r="L82" s="4" t="s">
         <v>2424</v>
       </c>
-      <c r="L82" t="s">
+      <c r="M82" t="s">
         <v>2435</v>
       </c>
-      <c r="M82" t="s">
-        <v>2446</v>
-      </c>
       <c r="N82" t="s">
+        <v>2446</v>
+      </c>
+      <c r="O82" t="s">
         <v>2426</v>
       </c>
-      <c r="O82" t="s">
-        <v>2446</v>
-      </c>
       <c r="P82" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2446</v>
+      </c>
+      <c r="Q82" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="83" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>277</v>
       </c>
@@ -33605,17 +33851,17 @@
         <v>278</v>
       </c>
       <c r="I83" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J83" t="s">
         <v>6</v>
       </c>
-      <c r="J83" t="s">
-        <v>49</v>
-      </c>
-      <c r="K83" s="4" t="s">
+      <c r="K83" t="s">
+        <v>49</v>
+      </c>
+      <c r="L83" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L83" t="s">
-        <v>2434</v>
-      </c>
       <c r="M83" t="s">
         <v>2434</v>
       </c>
@@ -33626,10 +33872,13 @@
         <v>2434</v>
       </c>
       <c r="P83" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2434</v>
+      </c>
+      <c r="Q83" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="84" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>283</v>
       </c>
@@ -33655,17 +33904,17 @@
         <v>278</v>
       </c>
       <c r="I84" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J84" t="s">
         <v>285</v>
       </c>
-      <c r="J84" t="s">
-        <v>49</v>
-      </c>
-      <c r="K84" s="4" t="s">
+      <c r="K84" t="s">
+        <v>49</v>
+      </c>
+      <c r="L84" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L84" t="s">
-        <v>2434</v>
-      </c>
       <c r="M84" t="s">
         <v>2434</v>
       </c>
@@ -33673,13 +33922,16 @@
         <v>2434</v>
       </c>
       <c r="O84" t="s">
+        <v>2434</v>
+      </c>
+      <c r="P84" t="s">
         <v>2461</v>
       </c>
-      <c r="P84" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q84" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="85" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>179</v>
       </c>
@@ -33705,31 +33957,34 @@
         <v>278</v>
       </c>
       <c r="I85" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J85" t="s">
         <v>177</v>
       </c>
-      <c r="J85" t="s">
-        <v>49</v>
-      </c>
-      <c r="K85" s="4" t="s">
+      <c r="K85" t="s">
+        <v>49</v>
+      </c>
+      <c r="L85" s="4" t="s">
         <v>2430</v>
       </c>
-      <c r="L85" t="s">
+      <c r="M85" t="s">
         <v>2443</v>
       </c>
-      <c r="M85" t="s">
+      <c r="N85" t="s">
         <v>2451</v>
       </c>
-      <c r="N85" t="s">
-        <v>2434</v>
-      </c>
       <c r="O85" t="s">
         <v>2434</v>
       </c>
       <c r="P85" t="s">
+        <v>2434</v>
+      </c>
+      <c r="Q85" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>227</v>
       </c>
@@ -33755,17 +34010,17 @@
         <v>271</v>
       </c>
       <c r="I86" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J86" t="s">
         <v>6</v>
       </c>
-      <c r="J86" t="s">
-        <v>49</v>
-      </c>
-      <c r="K86" s="4" t="s">
+      <c r="K86" t="s">
+        <v>49</v>
+      </c>
+      <c r="L86" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L86" t="s">
-        <v>2434</v>
-      </c>
       <c r="M86" t="s">
         <v>2434</v>
       </c>
@@ -33776,10 +34031,13 @@
         <v>2434</v>
       </c>
       <c r="P86" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2434</v>
+      </c>
+      <c r="Q86" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="87" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>228</v>
       </c>
@@ -33805,17 +34063,17 @@
         <v>271</v>
       </c>
       <c r="I87" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J87" t="s">
         <v>6</v>
       </c>
-      <c r="J87" t="s">
-        <v>49</v>
-      </c>
-      <c r="K87" s="4" t="s">
+      <c r="K87" t="s">
+        <v>49</v>
+      </c>
+      <c r="L87" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L87" t="s">
-        <v>2434</v>
-      </c>
       <c r="M87" t="s">
         <v>2434</v>
       </c>
@@ -33826,10 +34084,13 @@
         <v>2434</v>
       </c>
       <c r="P87" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2434</v>
+      </c>
+      <c r="Q87" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="88" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>251</v>
       </c>
@@ -33855,17 +34116,17 @@
         <v>271</v>
       </c>
       <c r="I88" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J88" t="s">
         <v>6</v>
       </c>
-      <c r="J88" t="s">
-        <v>49</v>
-      </c>
-      <c r="K88" s="4" t="s">
+      <c r="K88" t="s">
+        <v>49</v>
+      </c>
+      <c r="L88" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L88" t="s">
-        <v>2434</v>
-      </c>
       <c r="M88" t="s">
         <v>2434</v>
       </c>
@@ -33873,13 +34134,16 @@
         <v>2434</v>
       </c>
       <c r="O88" t="s">
+        <v>2434</v>
+      </c>
+      <c r="P88" t="s">
         <v>2461</v>
       </c>
-      <c r="P88" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q88" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="89" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>270</v>
       </c>
@@ -33905,17 +34169,17 @@
         <v>271</v>
       </c>
       <c r="I89" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J89" t="s">
         <v>6</v>
       </c>
-      <c r="J89" t="s">
-        <v>49</v>
-      </c>
-      <c r="K89" s="4" t="s">
+      <c r="K89" t="s">
+        <v>49</v>
+      </c>
+      <c r="L89" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L89" t="s">
-        <v>2434</v>
-      </c>
       <c r="M89" t="s">
         <v>2434</v>
       </c>
@@ -33923,13 +34187,16 @@
         <v>2434</v>
       </c>
       <c r="O89" t="s">
+        <v>2434</v>
+      </c>
+      <c r="P89" t="s">
         <v>2462</v>
       </c>
-      <c r="P89" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q89" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="90" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>276</v>
       </c>
@@ -33955,17 +34222,17 @@
         <v>271</v>
       </c>
       <c r="I90" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J90" t="s">
         <v>6</v>
       </c>
-      <c r="J90" t="s">
-        <v>49</v>
-      </c>
-      <c r="K90" s="4" t="s">
+      <c r="K90" t="s">
+        <v>49</v>
+      </c>
+      <c r="L90" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L90" t="s">
-        <v>2434</v>
-      </c>
       <c r="M90" t="s">
         <v>2434</v>
       </c>
@@ -33976,10 +34243,13 @@
         <v>2434</v>
       </c>
       <c r="P90" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2434</v>
+      </c>
+      <c r="Q90" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="91" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>282</v>
       </c>
@@ -34005,17 +34275,17 @@
         <v>271</v>
       </c>
       <c r="I91" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J91" t="s">
         <v>6</v>
       </c>
-      <c r="J91" t="s">
-        <v>49</v>
-      </c>
-      <c r="K91" s="4" t="s">
+      <c r="K91" t="s">
+        <v>49</v>
+      </c>
+      <c r="L91" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L91" t="s">
-        <v>2434</v>
-      </c>
       <c r="M91" t="s">
         <v>2434</v>
       </c>
@@ -34026,10 +34296,13 @@
         <v>2434</v>
       </c>
       <c r="P91" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2434</v>
+      </c>
+      <c r="Q91" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="92" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>229</v>
       </c>
@@ -34055,31 +34328,34 @@
         <v>271</v>
       </c>
       <c r="I92" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J92" t="s">
         <v>6</v>
       </c>
-      <c r="J92" t="s">
-        <v>49</v>
-      </c>
-      <c r="K92" s="4" t="s">
+      <c r="K92" t="s">
+        <v>49</v>
+      </c>
+      <c r="L92" s="4" t="s">
         <v>2433</v>
       </c>
-      <c r="L92" t="s">
+      <c r="M92" t="s">
         <v>2444</v>
       </c>
-      <c r="M92" t="s">
+      <c r="N92" t="s">
         <v>2454</v>
       </c>
-      <c r="N92" t="s">
-        <v>2434</v>
-      </c>
       <c r="O92" t="s">
         <v>2434</v>
       </c>
       <c r="P92" t="s">
+        <v>2434</v>
+      </c>
+      <c r="Q92" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>249</v>
       </c>
@@ -34105,31 +34381,34 @@
         <v>2570</v>
       </c>
       <c r="I93" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J93" t="s">
         <v>6</v>
       </c>
-      <c r="J93" t="s">
-        <v>49</v>
-      </c>
-      <c r="K93" s="4" t="s">
+      <c r="K93" t="s">
+        <v>49</v>
+      </c>
+      <c r="L93" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L93" t="s">
-        <v>2434</v>
-      </c>
       <c r="M93" t="s">
+        <v>2434</v>
+      </c>
+      <c r="N93" t="s">
         <v>2452</v>
       </c>
-      <c r="N93" t="s">
-        <v>2434</v>
-      </c>
       <c r="O93" t="s">
         <v>2434</v>
       </c>
       <c r="P93" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2434</v>
+      </c>
+      <c r="Q93" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="94" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>252</v>
       </c>
@@ -34155,17 +34434,17 @@
         <v>2570</v>
       </c>
       <c r="I94" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J94" t="s">
         <v>6</v>
       </c>
-      <c r="J94" t="s">
-        <v>49</v>
-      </c>
-      <c r="K94" s="4" t="s">
+      <c r="K94" t="s">
+        <v>49</v>
+      </c>
+      <c r="L94" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L94" t="s">
-        <v>2434</v>
-      </c>
       <c r="M94" t="s">
         <v>2434</v>
       </c>
@@ -34176,10 +34455,13 @@
         <v>2434</v>
       </c>
       <c r="P94" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2434</v>
+      </c>
+      <c r="Q94" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="95" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>254</v>
       </c>
@@ -34205,17 +34487,17 @@
         <v>2570</v>
       </c>
       <c r="I95" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J95" t="s">
         <v>6</v>
       </c>
-      <c r="J95" t="s">
-        <v>49</v>
-      </c>
-      <c r="K95" s="4" t="s">
+      <c r="K95" t="s">
+        <v>49</v>
+      </c>
+      <c r="L95" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L95" t="s">
-        <v>2434</v>
-      </c>
       <c r="M95" t="s">
         <v>2434</v>
       </c>
@@ -34226,10 +34508,13 @@
         <v>2434</v>
       </c>
       <c r="P95" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2434</v>
+      </c>
+      <c r="Q95" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="96" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>225</v>
       </c>
@@ -34255,31 +34540,34 @@
         <v>2575</v>
       </c>
       <c r="I96" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J96" t="s">
         <v>6</v>
       </c>
-      <c r="J96" t="s">
-        <v>49</v>
-      </c>
-      <c r="K96" s="4" t="s">
+      <c r="K96" t="s">
+        <v>49</v>
+      </c>
+      <c r="L96" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L96" t="s">
-        <v>2434</v>
-      </c>
       <c r="M96" t="s">
+        <v>2434</v>
+      </c>
+      <c r="N96" t="s">
         <v>2452</v>
       </c>
-      <c r="N96" t="s">
-        <v>2434</v>
-      </c>
       <c r="O96" t="s">
         <v>2434</v>
       </c>
       <c r="P96" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2434</v>
+      </c>
+      <c r="Q96" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="97" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>226</v>
       </c>
@@ -34305,17 +34593,17 @@
         <v>2575</v>
       </c>
       <c r="I97" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J97" t="s">
         <v>6</v>
       </c>
-      <c r="J97" t="s">
-        <v>49</v>
-      </c>
-      <c r="K97" s="4" t="s">
+      <c r="K97" t="s">
+        <v>49</v>
+      </c>
+      <c r="L97" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L97" t="s">
-        <v>2434</v>
-      </c>
       <c r="M97" t="s">
         <v>2434</v>
       </c>
@@ -34326,10 +34614,13 @@
         <v>2434</v>
       </c>
       <c r="P97" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2434</v>
+      </c>
+      <c r="Q97" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="98" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>269</v>
       </c>
@@ -34355,17 +34646,17 @@
         <v>2577</v>
       </c>
       <c r="I98" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J98" t="s">
         <v>6</v>
       </c>
-      <c r="J98" t="s">
-        <v>49</v>
-      </c>
-      <c r="K98" s="4" t="s">
+      <c r="K98" t="s">
+        <v>49</v>
+      </c>
+      <c r="L98" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L98" t="s">
-        <v>2434</v>
-      </c>
       <c r="M98" t="s">
         <v>2434</v>
       </c>
@@ -34376,10 +34667,13 @@
         <v>2434</v>
       </c>
       <c r="P98" t="s">
+        <v>2434</v>
+      </c>
+      <c r="Q98" t="s">
         <v>2340</v>
       </c>
     </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>224</v>
       </c>
@@ -34405,31 +34699,34 @@
         <v>2574</v>
       </c>
       <c r="I99" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J99" t="s">
         <v>6</v>
       </c>
-      <c r="J99" t="s">
-        <v>49</v>
-      </c>
-      <c r="K99" s="4" t="s">
+      <c r="K99" t="s">
+        <v>49</v>
+      </c>
+      <c r="L99" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L99" t="s">
-        <v>2434</v>
-      </c>
       <c r="M99" t="s">
+        <v>2434</v>
+      </c>
+      <c r="N99" t="s">
         <v>2452</v>
       </c>
-      <c r="N99" t="s">
-        <v>2434</v>
-      </c>
       <c r="O99" t="s">
         <v>2434</v>
       </c>
       <c r="P99" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2434</v>
+      </c>
+      <c r="Q99" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="100" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>275</v>
       </c>
@@ -34455,17 +34752,17 @@
         <v>2565</v>
       </c>
       <c r="I100" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J100" t="s">
         <v>2564</v>
       </c>
-      <c r="J100" t="s">
-        <v>49</v>
-      </c>
-      <c r="K100" s="4" t="s">
+      <c r="K100" t="s">
+        <v>49</v>
+      </c>
+      <c r="L100" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L100" t="s">
-        <v>2434</v>
-      </c>
       <c r="M100" t="s">
         <v>2434</v>
       </c>
@@ -34476,10 +34773,13 @@
         <v>2434</v>
       </c>
       <c r="P100" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2434</v>
+      </c>
+      <c r="Q100" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="101" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>56</v>
       </c>
@@ -34505,31 +34805,34 @@
         <v>57</v>
       </c>
       <c r="I101" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J101" t="s">
         <v>6</v>
       </c>
-      <c r="J101" t="s">
-        <v>49</v>
-      </c>
-      <c r="K101" s="4" t="s">
+      <c r="K101" t="s">
+        <v>49</v>
+      </c>
+      <c r="L101" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L101" t="s">
-        <v>2434</v>
-      </c>
       <c r="M101" t="s">
         <v>2434</v>
       </c>
       <c r="N101" t="s">
+        <v>2434</v>
+      </c>
+      <c r="O101" t="s">
         <v>2456</v>
       </c>
-      <c r="O101" t="s">
-        <v>2434</v>
-      </c>
       <c r="P101" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="102" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2434</v>
+      </c>
+      <c r="Q101" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="102" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>140</v>
       </c>
@@ -34555,31 +34858,34 @@
         <v>142</v>
       </c>
       <c r="I102" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J102" t="s">
         <v>6</v>
       </c>
-      <c r="J102" t="s">
-        <v>49</v>
-      </c>
-      <c r="K102" s="4" t="s">
+      <c r="K102" t="s">
+        <v>49</v>
+      </c>
+      <c r="L102" s="4" t="s">
         <v>2426</v>
       </c>
-      <c r="L102" t="s">
+      <c r="M102" t="s">
         <v>2437</v>
       </c>
-      <c r="M102" t="s">
-        <v>2446</v>
-      </c>
       <c r="N102" t="s">
+        <v>2446</v>
+      </c>
+      <c r="O102" t="s">
         <v>2426</v>
       </c>
-      <c r="O102" t="s">
-        <v>2446</v>
-      </c>
       <c r="P102" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="103" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2446</v>
+      </c>
+      <c r="Q102" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="103" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>52</v>
       </c>
@@ -34605,31 +34911,34 @@
         <v>53</v>
       </c>
       <c r="I103" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J103" t="s">
         <v>6</v>
       </c>
-      <c r="J103" t="s">
-        <v>49</v>
-      </c>
-      <c r="K103" s="4" t="s">
+      <c r="K103" t="s">
+        <v>49</v>
+      </c>
+      <c r="L103" s="4" t="s">
         <v>2424</v>
       </c>
-      <c r="L103" t="s">
+      <c r="M103" t="s">
         <v>2435</v>
       </c>
-      <c r="M103" t="s">
-        <v>2446</v>
-      </c>
       <c r="N103" t="s">
+        <v>2446</v>
+      </c>
+      <c r="O103" t="s">
         <v>2426</v>
       </c>
-      <c r="O103" t="s">
-        <v>2446</v>
-      </c>
       <c r="P103" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="104" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2446</v>
+      </c>
+      <c r="Q103" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="104" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>293</v>
       </c>
@@ -34655,31 +34964,34 @@
         <v>2571</v>
       </c>
       <c r="I104" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J104" t="s">
         <v>48</v>
       </c>
-      <c r="J104" t="s">
-        <v>49</v>
-      </c>
-      <c r="K104" s="4" t="s">
+      <c r="K104" t="s">
+        <v>49</v>
+      </c>
+      <c r="L104" s="4" t="s">
         <v>2426</v>
       </c>
-      <c r="L104" t="s">
+      <c r="M104" t="s">
         <v>2438</v>
       </c>
-      <c r="M104" t="s">
-        <v>2446</v>
-      </c>
       <c r="N104" t="s">
+        <v>2446</v>
+      </c>
+      <c r="O104" t="s">
         <v>2426</v>
       </c>
-      <c r="O104" t="s">
-        <v>2446</v>
-      </c>
       <c r="P104" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="105" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2446</v>
+      </c>
+      <c r="Q104" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="105" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>65</v>
       </c>
@@ -34705,31 +35017,34 @@
         <v>67</v>
       </c>
       <c r="I105" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J105" t="s">
         <v>68</v>
       </c>
-      <c r="J105" t="s">
-        <v>49</v>
-      </c>
-      <c r="K105" s="4" t="s">
+      <c r="K105" t="s">
+        <v>49</v>
+      </c>
+      <c r="L105" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L105" t="s">
-        <v>2434</v>
-      </c>
       <c r="M105" t="s">
         <v>2434</v>
       </c>
       <c r="N105" t="s">
+        <v>2434</v>
+      </c>
+      <c r="O105" t="s">
         <v>2456</v>
       </c>
-      <c r="O105" t="s">
-        <v>2434</v>
-      </c>
       <c r="P105" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="106" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2434</v>
+      </c>
+      <c r="Q105" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="106" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>129</v>
       </c>
@@ -34755,17 +35070,17 @@
         <v>128</v>
       </c>
       <c r="I106" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J106" t="s">
         <v>6</v>
       </c>
-      <c r="J106" t="s">
-        <v>49</v>
-      </c>
-      <c r="K106" s="4" t="s">
+      <c r="K106" t="s">
+        <v>49</v>
+      </c>
+      <c r="L106" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L106" t="s">
-        <v>2434</v>
-      </c>
       <c r="M106" t="s">
         <v>2434</v>
       </c>
@@ -34776,10 +35091,13 @@
         <v>2434</v>
       </c>
       <c r="P106" t="s">
+        <v>2434</v>
+      </c>
+      <c r="Q106" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="107" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>134</v>
       </c>
@@ -34805,17 +35123,17 @@
         <v>128</v>
       </c>
       <c r="I107" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J107" t="s">
         <v>6</v>
       </c>
-      <c r="J107" t="s">
-        <v>49</v>
-      </c>
-      <c r="K107" s="4" t="s">
+      <c r="K107" t="s">
+        <v>49</v>
+      </c>
+      <c r="L107" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L107" t="s">
-        <v>2434</v>
-      </c>
       <c r="M107" t="s">
         <v>2434</v>
       </c>
@@ -34826,10 +35144,13 @@
         <v>2434</v>
       </c>
       <c r="P107" t="s">
+        <v>2434</v>
+      </c>
+      <c r="Q107" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="108" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>300</v>
       </c>
@@ -34855,17 +35176,17 @@
         <v>128</v>
       </c>
       <c r="I108" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J108" t="s">
         <v>301</v>
       </c>
-      <c r="J108" t="s">
-        <v>49</v>
-      </c>
-      <c r="K108" s="4" t="s">
+      <c r="K108" t="s">
+        <v>49</v>
+      </c>
+      <c r="L108" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L108" t="s">
-        <v>2434</v>
-      </c>
       <c r="M108" t="s">
         <v>2434</v>
       </c>
@@ -34876,10 +35197,13 @@
         <v>2434</v>
       </c>
       <c r="P108" t="s">
+        <v>2434</v>
+      </c>
+      <c r="Q108" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="109" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>126</v>
       </c>
@@ -34905,31 +35229,34 @@
         <v>128</v>
       </c>
       <c r="I109" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J109" t="s">
         <v>6</v>
       </c>
-      <c r="J109" t="s">
-        <v>49</v>
-      </c>
-      <c r="K109" s="4" t="s">
+      <c r="K109" t="s">
+        <v>49</v>
+      </c>
+      <c r="L109" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L109" t="s">
-        <v>2434</v>
-      </c>
       <c r="M109" t="s">
         <v>2434</v>
       </c>
       <c r="N109" t="s">
+        <v>2434</v>
+      </c>
+      <c r="O109" t="s">
         <v>2456</v>
       </c>
-      <c r="O109" t="s">
-        <v>2434</v>
-      </c>
       <c r="P109" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="110" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2434</v>
+      </c>
+      <c r="Q109" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="110" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>135</v>
       </c>
@@ -34955,17 +35282,17 @@
         <v>128</v>
       </c>
       <c r="I110" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J110" t="s">
         <v>6</v>
       </c>
-      <c r="J110" t="s">
-        <v>49</v>
-      </c>
-      <c r="K110" s="4" t="s">
+      <c r="K110" t="s">
+        <v>49</v>
+      </c>
+      <c r="L110" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L110" t="s">
-        <v>2434</v>
-      </c>
       <c r="M110" t="s">
         <v>2434</v>
       </c>
@@ -34976,10 +35303,13 @@
         <v>2434</v>
       </c>
       <c r="P110" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="111" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2434</v>
+      </c>
+      <c r="Q110" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="111" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>138</v>
       </c>
@@ -35005,17 +35335,17 @@
         <v>139</v>
       </c>
       <c r="I111" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J111" t="s">
         <v>6</v>
       </c>
-      <c r="J111" t="s">
-        <v>49</v>
-      </c>
-      <c r="K111" s="4" t="s">
+      <c r="K111" t="s">
+        <v>49</v>
+      </c>
+      <c r="L111" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L111" t="s">
-        <v>2434</v>
-      </c>
       <c r="M111" t="s">
         <v>2434</v>
       </c>
@@ -35026,10 +35356,13 @@
         <v>2434</v>
       </c>
       <c r="P111" t="s">
+        <v>2434</v>
+      </c>
+      <c r="Q111" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="112" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>279</v>
       </c>
@@ -35055,31 +35388,34 @@
         <v>281</v>
       </c>
       <c r="I112" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J112" t="s">
         <v>6</v>
       </c>
-      <c r="J112" t="s">
-        <v>49</v>
-      </c>
-      <c r="K112" s="4" t="s">
+      <c r="K112" t="s">
+        <v>49</v>
+      </c>
+      <c r="L112" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L112" t="s">
-        <v>2434</v>
-      </c>
       <c r="M112" t="s">
+        <v>2434</v>
+      </c>
+      <c r="N112" t="s">
         <v>2455</v>
       </c>
-      <c r="N112" t="s">
-        <v>2434</v>
-      </c>
       <c r="O112" t="s">
         <v>2434</v>
       </c>
       <c r="P112" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="113" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2434</v>
+      </c>
+      <c r="Q112" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="113" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>272</v>
       </c>
@@ -35105,17 +35441,17 @@
         <v>274</v>
       </c>
       <c r="I113" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J113" t="s">
         <v>6</v>
       </c>
-      <c r="J113" t="s">
-        <v>49</v>
-      </c>
-      <c r="K113" s="4" t="s">
+      <c r="K113" t="s">
+        <v>49</v>
+      </c>
+      <c r="L113" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L113" t="s">
-        <v>2434</v>
-      </c>
       <c r="M113" t="s">
         <v>2434</v>
       </c>
@@ -35126,10 +35462,13 @@
         <v>2434</v>
       </c>
       <c r="P113" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="114" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2434</v>
+      </c>
+      <c r="Q113" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="114" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>298</v>
       </c>
@@ -35155,31 +35494,34 @@
         <v>108</v>
       </c>
       <c r="I114" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J114" t="s">
         <v>296</v>
       </c>
-      <c r="J114" t="s">
-        <v>49</v>
-      </c>
-      <c r="K114" s="4" t="s">
+      <c r="K114" t="s">
+        <v>49</v>
+      </c>
+      <c r="L114" s="4" t="s">
         <v>2432</v>
       </c>
-      <c r="L114" t="s">
+      <c r="M114" t="s">
         <v>2444</v>
       </c>
-      <c r="M114" t="s">
+      <c r="N114" t="s">
         <v>2453</v>
       </c>
-      <c r="N114" t="s">
-        <v>2434</v>
-      </c>
       <c r="O114" t="s">
         <v>2434</v>
       </c>
       <c r="P114" t="s">
+        <v>2434</v>
+      </c>
+      <c r="Q114" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="115" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>295</v>
       </c>
@@ -35205,17 +35547,17 @@
         <v>108</v>
       </c>
       <c r="I115" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J115" t="s">
         <v>296</v>
       </c>
-      <c r="J115" t="s">
-        <v>49</v>
-      </c>
-      <c r="K115" s="4" t="s">
+      <c r="K115" t="s">
+        <v>49</v>
+      </c>
+      <c r="L115" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L115" t="s">
-        <v>2434</v>
-      </c>
       <c r="M115" t="s">
         <v>2434</v>
       </c>
@@ -35226,10 +35568,13 @@
         <v>2434</v>
       </c>
       <c r="P115" t="s">
+        <v>2434</v>
+      </c>
+      <c r="Q115" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="116" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>106</v>
       </c>
@@ -35255,31 +35600,34 @@
         <v>108</v>
       </c>
       <c r="I116" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J116" t="s">
         <v>6</v>
       </c>
-      <c r="J116" t="s">
-        <v>49</v>
-      </c>
-      <c r="K116" s="4" t="s">
+      <c r="K116" t="s">
+        <v>49</v>
+      </c>
+      <c r="L116" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L116" t="s">
-        <v>2434</v>
-      </c>
       <c r="M116" t="s">
         <v>2434</v>
       </c>
       <c r="N116" t="s">
+        <v>2434</v>
+      </c>
+      <c r="O116" t="s">
         <v>2456</v>
       </c>
-      <c r="O116" t="s">
-        <v>2434</v>
-      </c>
       <c r="P116" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="117" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2434</v>
+      </c>
+      <c r="Q116" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="117" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>150</v>
       </c>
@@ -35305,17 +35653,17 @@
         <v>152</v>
       </c>
       <c r="I117" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J117" t="s">
         <v>6</v>
       </c>
-      <c r="J117" t="s">
-        <v>49</v>
-      </c>
-      <c r="K117" s="4" t="s">
+      <c r="K117" t="s">
+        <v>49</v>
+      </c>
+      <c r="L117" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L117" t="s">
-        <v>2434</v>
-      </c>
       <c r="M117" t="s">
         <v>2434</v>
       </c>
@@ -35326,10 +35674,13 @@
         <v>2434</v>
       </c>
       <c r="P117" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="118" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2434</v>
+      </c>
+      <c r="Q117" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="118" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>153</v>
       </c>
@@ -35355,17 +35706,17 @@
         <v>152</v>
       </c>
       <c r="I118" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J118" t="s">
         <v>6</v>
       </c>
-      <c r="J118" t="s">
-        <v>49</v>
-      </c>
-      <c r="K118" s="4" t="s">
+      <c r="K118" t="s">
+        <v>49</v>
+      </c>
+      <c r="L118" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L118" t="s">
-        <v>2434</v>
-      </c>
       <c r="M118" t="s">
         <v>2434</v>
       </c>
@@ -35376,10 +35727,13 @@
         <v>2434</v>
       </c>
       <c r="P118" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="119" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2434</v>
+      </c>
+      <c r="Q118" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="119" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>2569</v>
       </c>
@@ -35405,17 +35759,17 @@
         <v>2572</v>
       </c>
       <c r="I119" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J119" t="s">
         <v>2573</v>
       </c>
-      <c r="J119" t="s">
-        <v>49</v>
-      </c>
-      <c r="K119" s="4" t="s">
+      <c r="K119" t="s">
+        <v>49</v>
+      </c>
+      <c r="L119" s="4" t="s">
         <v>2462</v>
       </c>
-      <c r="L119" t="s">
-        <v>2434</v>
-      </c>
       <c r="M119" t="s">
         <v>2434</v>
       </c>
@@ -35426,10 +35780,13 @@
         <v>2434</v>
       </c>
       <c r="P119" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="120" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2434</v>
+      </c>
+      <c r="Q119" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="120" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>100</v>
       </c>
@@ -35455,31 +35812,34 @@
         <v>102</v>
       </c>
       <c r="I120" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J120" t="s">
         <v>103</v>
       </c>
-      <c r="J120" t="s">
-        <v>49</v>
-      </c>
-      <c r="K120" s="4" t="s">
+      <c r="K120" t="s">
+        <v>49</v>
+      </c>
+      <c r="L120" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L120" t="s">
-        <v>2434</v>
-      </c>
       <c r="M120" t="s">
         <v>2434</v>
       </c>
       <c r="N120" t="s">
+        <v>2434</v>
+      </c>
+      <c r="O120" t="s">
         <v>2456</v>
       </c>
-      <c r="O120" t="s">
-        <v>2434</v>
-      </c>
       <c r="P120" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="121" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2434</v>
+      </c>
+      <c r="Q120" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="121" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>61</v>
       </c>
@@ -35505,31 +35865,34 @@
         <v>62</v>
       </c>
       <c r="I121" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J121" t="s">
         <v>6</v>
       </c>
-      <c r="J121" t="s">
-        <v>49</v>
-      </c>
-      <c r="K121" s="4" t="s">
+      <c r="K121" t="s">
+        <v>49</v>
+      </c>
+      <c r="L121" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L121" t="s">
-        <v>2434</v>
-      </c>
       <c r="M121" t="s">
         <v>2434</v>
       </c>
       <c r="N121" t="s">
+        <v>2434</v>
+      </c>
+      <c r="O121" t="s">
         <v>2456</v>
       </c>
-      <c r="O121" t="s">
-        <v>2434</v>
-      </c>
       <c r="P121" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="122" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2434</v>
+      </c>
+      <c r="Q121" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="122" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>85</v>
       </c>
@@ -35555,31 +35918,34 @@
         <v>87</v>
       </c>
       <c r="I122" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J122" t="s">
         <v>6</v>
       </c>
-      <c r="J122" t="s">
-        <v>49</v>
-      </c>
-      <c r="K122" s="4" t="s">
+      <c r="K122" t="s">
+        <v>49</v>
+      </c>
+      <c r="L122" s="4" t="s">
         <v>2424</v>
       </c>
-      <c r="L122" t="s">
+      <c r="M122" t="s">
         <v>2435</v>
       </c>
-      <c r="M122" t="s">
-        <v>2446</v>
-      </c>
       <c r="N122" t="s">
+        <v>2446</v>
+      </c>
+      <c r="O122" t="s">
         <v>2426</v>
       </c>
-      <c r="O122" t="s">
-        <v>2446</v>
-      </c>
       <c r="P122" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="123" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2446</v>
+      </c>
+      <c r="Q122" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="123" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>88</v>
       </c>
@@ -35605,31 +35971,34 @@
         <v>87</v>
       </c>
       <c r="I123" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J123" t="s">
         <v>6</v>
       </c>
-      <c r="J123" t="s">
-        <v>49</v>
-      </c>
-      <c r="K123" s="4" t="s">
+      <c r="K123" t="s">
+        <v>49</v>
+      </c>
+      <c r="L123" s="4" t="s">
         <v>2424</v>
       </c>
-      <c r="L123" t="s">
+      <c r="M123" t="s">
         <v>2435</v>
       </c>
-      <c r="M123" t="s">
-        <v>2446</v>
-      </c>
       <c r="N123" t="s">
+        <v>2446</v>
+      </c>
+      <c r="O123" t="s">
         <v>2426</v>
       </c>
-      <c r="O123" t="s">
-        <v>2446</v>
-      </c>
       <c r="P123" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="124" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2446</v>
+      </c>
+      <c r="Q123" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="124" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>90</v>
       </c>
@@ -35655,31 +36024,34 @@
         <v>87</v>
       </c>
       <c r="I124" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J124" t="s">
         <v>6</v>
       </c>
-      <c r="J124" t="s">
-        <v>49</v>
-      </c>
-      <c r="K124" s="4" t="s">
+      <c r="K124" t="s">
+        <v>49</v>
+      </c>
+      <c r="L124" s="4" t="s">
         <v>2424</v>
       </c>
-      <c r="L124" t="s">
+      <c r="M124" t="s">
         <v>2435</v>
       </c>
-      <c r="M124" t="s">
-        <v>2446</v>
-      </c>
       <c r="N124" t="s">
+        <v>2446</v>
+      </c>
+      <c r="O124" t="s">
         <v>2426</v>
       </c>
-      <c r="O124" t="s">
-        <v>2446</v>
-      </c>
       <c r="P124" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="125" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2446</v>
+      </c>
+      <c r="Q124" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="125" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>92</v>
       </c>
@@ -35705,31 +36077,34 @@
         <v>87</v>
       </c>
       <c r="I125" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J125" t="s">
         <v>6</v>
       </c>
-      <c r="J125" t="s">
-        <v>49</v>
-      </c>
-      <c r="K125" s="4" t="s">
+      <c r="K125" t="s">
+        <v>49</v>
+      </c>
+      <c r="L125" s="4" t="s">
         <v>2424</v>
       </c>
-      <c r="L125" t="s">
+      <c r="M125" t="s">
         <v>2435</v>
       </c>
-      <c r="M125" t="s">
-        <v>2446</v>
-      </c>
       <c r="N125" t="s">
+        <v>2446</v>
+      </c>
+      <c r="O125" t="s">
         <v>2426</v>
       </c>
-      <c r="O125" t="s">
-        <v>2446</v>
-      </c>
       <c r="P125" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="126" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2446</v>
+      </c>
+      <c r="Q125" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="126" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>94</v>
       </c>
@@ -35755,31 +36130,34 @@
         <v>62</v>
       </c>
       <c r="I126" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J126" t="s">
         <v>6</v>
       </c>
-      <c r="J126" t="s">
-        <v>49</v>
-      </c>
-      <c r="K126" s="4" t="s">
+      <c r="K126" t="s">
+        <v>49</v>
+      </c>
+      <c r="L126" s="4" t="s">
         <v>2425</v>
       </c>
-      <c r="L126" t="s">
+      <c r="M126" t="s">
         <v>2440</v>
       </c>
-      <c r="M126" t="s">
+      <c r="N126" t="s">
         <v>2447</v>
       </c>
-      <c r="N126" t="s">
+      <c r="O126" t="s">
         <v>2457</v>
       </c>
-      <c r="O126" t="s">
+      <c r="P126" t="s">
         <v>2460</v>
       </c>
-      <c r="P126" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="127" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q126" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="127" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>112</v>
       </c>
@@ -35805,31 +36183,34 @@
         <v>62</v>
       </c>
       <c r="I127" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J127" t="s">
         <v>6</v>
       </c>
-      <c r="J127" t="s">
-        <v>49</v>
-      </c>
-      <c r="K127" s="4" t="s">
+      <c r="K127" t="s">
+        <v>49</v>
+      </c>
+      <c r="L127" s="4" t="s">
         <v>2424</v>
       </c>
-      <c r="L127" t="s">
+      <c r="M127" t="s">
         <v>2436</v>
       </c>
-      <c r="M127" t="s">
+      <c r="N127" t="s">
         <v>2448</v>
       </c>
-      <c r="N127" t="s">
+      <c r="O127" t="s">
         <v>2426</v>
       </c>
-      <c r="O127" t="s">
-        <v>2446</v>
-      </c>
       <c r="P127" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="128" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2446</v>
+      </c>
+      <c r="Q127" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="128" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>114</v>
       </c>
@@ -35855,31 +36236,34 @@
         <v>62</v>
       </c>
       <c r="I128" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J128" t="s">
         <v>6</v>
       </c>
-      <c r="J128" t="s">
-        <v>49</v>
-      </c>
-      <c r="K128" s="4" t="s">
+      <c r="K128" t="s">
+        <v>49</v>
+      </c>
+      <c r="L128" s="4" t="s">
         <v>2424</v>
       </c>
-      <c r="L128" t="s">
+      <c r="M128" t="s">
         <v>2436</v>
       </c>
-      <c r="M128" t="s">
+      <c r="N128" t="s">
         <v>2448</v>
       </c>
-      <c r="N128" t="s">
+      <c r="O128" t="s">
         <v>2426</v>
       </c>
-      <c r="O128" t="s">
-        <v>2446</v>
-      </c>
       <c r="P128" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="129" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2446</v>
+      </c>
+      <c r="Q128" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="129" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>115</v>
       </c>
@@ -35905,31 +36289,34 @@
         <v>117</v>
       </c>
       <c r="I129" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J129" t="s">
         <v>6</v>
       </c>
-      <c r="J129" t="s">
-        <v>49</v>
-      </c>
-      <c r="K129" s="4" t="s">
+      <c r="K129" t="s">
+        <v>49</v>
+      </c>
+      <c r="L129" s="4" t="s">
         <v>2424</v>
       </c>
-      <c r="L129" t="s">
+      <c r="M129" t="s">
         <v>2436</v>
       </c>
-      <c r="M129" t="s">
+      <c r="N129" t="s">
         <v>2448</v>
       </c>
-      <c r="N129" t="s">
+      <c r="O129" t="s">
         <v>2426</v>
       </c>
-      <c r="O129" t="s">
-        <v>2446</v>
-      </c>
       <c r="P129" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="130" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2446</v>
+      </c>
+      <c r="Q129" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="130" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>125</v>
       </c>
@@ -35955,31 +36342,34 @@
         <v>117</v>
       </c>
       <c r="I130" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J130" t="s">
         <v>6</v>
       </c>
-      <c r="J130" t="s">
-        <v>49</v>
-      </c>
-      <c r="K130" s="4" t="s">
+      <c r="K130" t="s">
+        <v>49</v>
+      </c>
+      <c r="L130" s="4" t="s">
         <v>2422</v>
       </c>
-      <c r="L130" t="s">
-        <v>2434</v>
-      </c>
       <c r="M130" t="s">
         <v>2434</v>
       </c>
       <c r="N130" t="s">
+        <v>2434</v>
+      </c>
+      <c r="O130" t="s">
         <v>2456</v>
       </c>
-      <c r="O130" t="s">
-        <v>2434</v>
-      </c>
       <c r="P130" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="131" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2434</v>
+      </c>
+      <c r="Q130" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="131" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>133</v>
       </c>
@@ -36005,31 +36395,34 @@
         <v>62</v>
       </c>
       <c r="I131" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J131" t="s">
         <v>6</v>
       </c>
-      <c r="J131" t="s">
-        <v>49</v>
-      </c>
-      <c r="K131" s="4" t="s">
+      <c r="K131" t="s">
+        <v>49</v>
+      </c>
+      <c r="L131" s="4" t="s">
         <v>2424</v>
       </c>
-      <c r="L131" t="s">
+      <c r="M131" t="s">
         <v>2436</v>
       </c>
-      <c r="M131" t="s">
+      <c r="N131" t="s">
         <v>2448</v>
       </c>
-      <c r="N131" t="s">
+      <c r="O131" t="s">
         <v>2426</v>
       </c>
-      <c r="O131" t="s">
-        <v>2446</v>
-      </c>
       <c r="P131" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="132" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2446</v>
+      </c>
+      <c r="Q131" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="132" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>137</v>
       </c>
@@ -36055,31 +36448,34 @@
         <v>62</v>
       </c>
       <c r="I132" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J132" t="s">
         <v>6</v>
       </c>
-      <c r="J132" t="s">
-        <v>49</v>
-      </c>
-      <c r="K132" s="4" t="s">
+      <c r="K132" t="s">
+        <v>49</v>
+      </c>
+      <c r="L132" s="4" t="s">
         <v>2424</v>
       </c>
-      <c r="L132" t="s">
+      <c r="M132" t="s">
         <v>2436</v>
       </c>
-      <c r="M132" t="s">
+      <c r="N132" t="s">
         <v>2448</v>
       </c>
-      <c r="N132" t="s">
+      <c r="O132" t="s">
         <v>2426</v>
       </c>
-      <c r="O132" t="s">
-        <v>2446</v>
-      </c>
       <c r="P132" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="133" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2446</v>
+      </c>
+      <c r="Q132" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="133" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>148</v>
       </c>
@@ -36105,31 +36501,34 @@
         <v>62</v>
       </c>
       <c r="I133" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J133" t="s">
         <v>103</v>
       </c>
-      <c r="J133" t="s">
-        <v>49</v>
-      </c>
-      <c r="K133" s="4" t="s">
+      <c r="K133" t="s">
+        <v>49</v>
+      </c>
+      <c r="L133" s="4" t="s">
         <v>2428</v>
       </c>
-      <c r="L133" t="s">
+      <c r="M133" t="s">
         <v>2440</v>
       </c>
-      <c r="M133" t="s">
-        <v>2446</v>
-      </c>
       <c r="N133" t="s">
+        <v>2446</v>
+      </c>
+      <c r="O133" t="s">
         <v>2426</v>
       </c>
-      <c r="O133" t="s">
-        <v>2446</v>
-      </c>
       <c r="P133" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="134" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2446</v>
+      </c>
+      <c r="Q133" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="134" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>213</v>
       </c>
@@ -36155,33 +36554,36 @@
         <v>2578</v>
       </c>
       <c r="I134" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J134" t="s">
         <v>6</v>
       </c>
-      <c r="J134" t="s">
-        <v>49</v>
-      </c>
-      <c r="K134" s="4" t="s">
+      <c r="K134" t="s">
+        <v>49</v>
+      </c>
+      <c r="L134" s="4" t="s">
         <v>2430</v>
       </c>
-      <c r="L134" t="s">
+      <c r="M134" t="s">
         <v>2443</v>
       </c>
-      <c r="M134" t="s">
+      <c r="N134" t="s">
         <v>2451</v>
       </c>
-      <c r="N134" t="s">
-        <v>2434</v>
-      </c>
       <c r="O134" t="s">
         <v>2434</v>
       </c>
       <c r="P134" t="s">
+        <v>2434</v>
+      </c>
+      <c r="Q134" t="s">
         <v>181</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P1" xr:uid="{B785887B-576B-4D81-AE70-D107EA8277F5}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P134">
+  <autoFilter ref="A1:Q1" xr:uid="{B785887B-576B-4D81-AE70-D107EA8277F5}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q134">
       <sortCondition ref="H1"/>
     </sortState>
   </autoFilter>

--- a/cirt_data.xlsx
+++ b/cirt_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ce1ebde9cded71ae/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="166" documentId="13_ncr:1_{C6350078-5CFC-4B20-8D31-D68148B331D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A0E237A-3892-4FBD-ABF0-177C512E6849}"/>
+  <xr:revisionPtr revIDLastSave="381" documentId="13_ncr:1_{C6350078-5CFC-4B20-8D31-D68148B331D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7652BA7E-9D2A-4F39-991C-96B793DF97D0}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{969D6A76-162A-4286-A653-6BBA36AECB0D}"/>
+    <workbookView xWindow="-16365" yWindow="-165" windowWidth="16530" windowHeight="28410" xr2:uid="{969D6A76-162A-4286-A653-6BBA36AECB0D}"/>
   </bookViews>
   <sheets>
     <sheet name="courses" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8333" uniqueCount="2616">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8381" uniqueCount="2640">
   <si>
     <t>Effective Communication: Writing</t>
   </si>
@@ -7886,6 +7886,78 @@
   </si>
   <si>
     <t>Fall 2026, Spring 2026, Spring 2025, Fall 2024-DTSC only</t>
+  </si>
+  <si>
+    <t>None during Fall 2024-Fall 2026</t>
+  </si>
+  <si>
+    <t>Fall 2026, Summer 2026, Spring 2026, Fall 2025, Summer 2025, Spring 2025, Fall 2024</t>
+  </si>
+  <si>
+    <t>Fall 2026, Spring 2026</t>
+  </si>
+  <si>
+    <t>Spring 2026, Fall 2025</t>
+  </si>
+  <si>
+    <t>Summer 2026, Fall 2025, Spring 2025</t>
+  </si>
+  <si>
+    <t>Fall 2026, Spring 2026, Summer 2025, Spring 2025, Fall 2024</t>
+  </si>
+  <si>
+    <t>Fall 2026, Spring 2026, Fall 2025, Summer 2025</t>
+  </si>
+  <si>
+    <t>Summer 2026, Fall 2025, Summer 2025, Spring 2025, Fall 2024</t>
+  </si>
+  <si>
+    <t>Fall 2026, Spring 2026, Summer 2025, Fall 2024</t>
+  </si>
+  <si>
+    <t>Fall 2026, Fall 2025, Spring 2025, Fall 2024</t>
+  </si>
+  <si>
+    <t>Spring 2026, Spring 2025, Fall 2024</t>
+  </si>
+  <si>
+    <t>Summer 2026, Summer 2025</t>
+  </si>
+  <si>
+    <t>Spring 2026, Fall 2025, Spring 2025</t>
+  </si>
+  <si>
+    <t>CYBR-5830-2257-001</t>
+  </si>
+  <si>
+    <t>Fall 2025, Spring 2025, Fall 2024</t>
+  </si>
+  <si>
+    <t>CYBR-5830-2251-002</t>
+  </si>
+  <si>
+    <t>CYBR-5830-2247-003</t>
+  </si>
+  <si>
+    <t>Embedded Cybersecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Embedded devices and IoT are all around us - they are involved in our nation's most critical infrastructure and industries, as well as deployed commonly across households and in businesses of all sizes. Such devices are known as Operational Technology (OT) – OT is vastly different from Information Technology (IT). Similarly, securing such products through OT security is worlds apart from IT security, the normal intention behind the term “cybersecurity”. The goal of this course is to expose students to a wide array of technologies, techniques, concepts, and regulations that are applicable to the world around them and valuable in their future security careers, regardless of where they end up. In this course, students should expect to learn the basics of secure product development and embedded/IoT systems, as well as cover the following additional topics: Asset threat modeling and design vulnerability assessment; Security testing and verification to identify implementation vulnerabilities (penetration testing, static analysis, fuzz testing, input/unit boundary analysis, etc.); Hardware hacking, reverse engineering, serial and wireless communications sniffing, side channel attacks (fault injection and power monitoring), and more; Post-market sales, implementation, maintenance, and End-of-Life/End-of-Service (Software Bill of Materials, VeX, Instructions for Use, in-field software updates, disclosures, agreements, etc.); Product security governance (organizational policies and procedures); and Global and U.S.-based product security regulatory and consensus standards (ISO/IEC, FDA, HSCC, Executive Orders, GDPR, HIPAA, MDR, AAMI, etc.) </t>
+  </si>
+  <si>
+    <t>The class will be a mixture of lecture, hands-on exercises, guest lectures from industry experts, and group learning and projects. NO PREREQUISITES ARE REQUIRED FOR THIS COURSE. All content and knowledge base required to be successful in this course will be covered and provided by the instructor. Optional textbooks can supplement the course, but no textbooks are required. All equipment needed will similarly be provided, except students will be expected to bring their own laptop.</t>
+  </si>
+  <si>
+    <t>Embedded devices and IoT are all around us - they are involved in our nation's most critical infrastructure and industries, as well as deployed commonly across households and in businesses of all sizes. Such devices are known as Operational Technology (OT) – OT is vastly different from Information Technology (IT). Similarly, securing such products through OT security is worlds apart from IT security, the normal intention behind the term “cybersecurity”. The goal of this course is to expose students to a wide array of technologies, techniques, concepts, and regulations that are applicable to the world around them and valuable in their future security or engineering careers, regardless of where they end up. In this course, students should expect to learn the basics of secure product development and embedded/IoT systems, as well as cover the following additional topics: Asset threat modeling and design vulnerability assessment; Security testing and verification to identify implementation vulnerabilities (penetration testing, static analysis, fuzz testing, software composition analysis, attack surface analysis, etc.); Hardware hacking, reverse engineering, serial and wireless communications sniffing, side channel attacks (fault injection and power monitoring), and more; Post-market sales, implementation, maintenance, and End-of-Life/End-of-Service (Software Bill of Materials, VEX, Instructions for Use, in-field software updates, disclosures, agreements, etc.); Product security governance (organizational policies and procedures); and Global and U.S.-based product security regulatory and consensus standards (ISO/IEC, FDA, HSCC, Executive Orders, GDPR, HIPAA, MDR, AAMI, etc.)</t>
+  </si>
+  <si>
+    <t>The class will be a mixture of lecture, hands-on exercises, guest lectures from industry experts, and group learning and projects. NO PREREQUISITES ARE REQUIRED FOR THIS COURSE. All content and knowledge base required to be successful in this course will be covered and provided by the instructor. Optional textbooks can supplement the course, but no textbooks are required. All equipment needed will similarly be provided, except students will be expected to bring their own laptops. This class will have its last meeting day on Friday, Dec. 5, 2025.</t>
+  </si>
+  <si>
+    <t>The class will be a mixture of lecture, hands-on exercises, guest lectures from industry experts, and group learning and projects. NO PREREQUISITES ARE REQUIRED FOR THIS COURSE. All content and knowledge base required to be successful in this course will be covered and provided by the instructor. Optional textbooks can supplement the course, but no textbooks are required. All equipment needed will similarly be provided, except students will be expected to bring their own laptops.</t>
+  </si>
+  <si>
+    <t>Fall 2026, Spring 2026, Fall 2025</t>
   </si>
 </sst>
 </file>
@@ -8392,7 +8464,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -8406,6 +8478,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -8462,6 +8535,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8785,10 +8862,9 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.6328125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10.81640625" style="1" customWidth="1"/>
-    <col min="3" max="4" width="10.81640625" style="1" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="10.81640625" style="3" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="11.54296875" style="1" hidden="1" customWidth="1"/>
+    <col min="2" max="4" width="10.81640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="10.81640625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="11.54296875" style="1" customWidth="1"/>
     <col min="7" max="7" width="62.6328125" style="1" customWidth="1"/>
     <col min="8" max="9" width="10.81640625" style="1" customWidth="1"/>
     <col min="10" max="15" width="22" style="1" customWidth="1"/>
@@ -19296,7 +19372,7 @@
         <v>1404</v>
       </c>
       <c r="G224" s="1" t="s">
-        <v>2514</v>
+        <v>2598</v>
       </c>
       <c r="H224" s="1" t="s">
         <v>1405</v>
@@ -19343,7 +19419,7 @@
         <v>1409</v>
       </c>
       <c r="G225" s="1" t="s">
-        <v>2514</v>
+        <v>2599</v>
       </c>
       <c r="H225" s="1" t="s">
         <v>1405</v>
@@ -19390,7 +19466,7 @@
         <v>268</v>
       </c>
       <c r="G226" s="1" t="s">
-        <v>2514</v>
+        <v>2596</v>
       </c>
       <c r="H226" s="1" t="s">
         <v>6</v>
@@ -19437,7 +19513,7 @@
         <v>1418</v>
       </c>
       <c r="G227" s="1" t="s">
-        <v>2514</v>
+        <v>46</v>
       </c>
       <c r="H227" s="1" t="s">
         <v>1419</v>
@@ -19484,7 +19560,7 @@
         <v>1424</v>
       </c>
       <c r="G228" s="1" t="s">
-        <v>2514</v>
+        <v>2598</v>
       </c>
       <c r="H228" s="1" t="s">
         <v>1425</v>
@@ -19531,7 +19607,7 @@
         <v>1430</v>
       </c>
       <c r="G229" s="1" t="s">
-        <v>2514</v>
+        <v>42</v>
       </c>
       <c r="H229" s="1" t="s">
         <v>1431</v>
@@ -19578,7 +19654,7 @@
         <v>1436</v>
       </c>
       <c r="G230" s="1" t="s">
-        <v>2514</v>
+        <v>2598</v>
       </c>
       <c r="H230" s="1" t="s">
         <v>1437</v>
@@ -19625,7 +19701,7 @@
         <v>344</v>
       </c>
       <c r="G231" s="1" t="s">
-        <v>2514</v>
+        <v>2616</v>
       </c>
       <c r="H231" s="1" t="s">
         <v>1442</v>
@@ -19672,7 +19748,7 @@
         <v>344</v>
       </c>
       <c r="G232" s="1" t="s">
-        <v>2514</v>
+        <v>2616</v>
       </c>
       <c r="H232" s="1" t="s">
         <v>1447</v>
@@ -19719,7 +19795,7 @@
         <v>344</v>
       </c>
       <c r="G233" s="1" t="s">
-        <v>2514</v>
+        <v>2616</v>
       </c>
       <c r="H233" s="1" t="s">
         <v>1452</v>
@@ -19766,7 +19842,7 @@
         <v>344</v>
       </c>
       <c r="G234" s="1" t="s">
-        <v>2514</v>
+        <v>2616</v>
       </c>
       <c r="H234" s="1" t="s">
         <v>1457</v>
@@ -19813,7 +19889,7 @@
         <v>1462</v>
       </c>
       <c r="G235" s="1" t="s">
-        <v>2514</v>
+        <v>42</v>
       </c>
       <c r="H235" s="1" t="s">
         <v>1463</v>
@@ -19860,7 +19936,7 @@
         <v>1022</v>
       </c>
       <c r="G236" s="1" t="s">
-        <v>2514</v>
+        <v>2597</v>
       </c>
       <c r="H236" s="1" t="s">
         <v>1468</v>
@@ -19907,7 +19983,7 @@
         <v>344</v>
       </c>
       <c r="G237" s="1" t="s">
-        <v>2514</v>
+        <v>2616</v>
       </c>
       <c r="H237" s="1" t="s">
         <v>1473</v>
@@ -19954,7 +20030,7 @@
         <v>1022</v>
       </c>
       <c r="G238" s="1" t="s">
-        <v>2514</v>
+        <v>2597</v>
       </c>
       <c r="H238" s="1" t="s">
         <v>1478</v>
@@ -20001,7 +20077,7 @@
         <v>1199</v>
       </c>
       <c r="G239" s="1" t="s">
-        <v>2514</v>
+        <v>43</v>
       </c>
       <c r="H239" s="1" t="s">
         <v>6</v>
@@ -20048,7 +20124,7 @@
         <v>344</v>
       </c>
       <c r="G240" s="1" t="s">
-        <v>2514</v>
+        <v>2616</v>
       </c>
       <c r="H240" s="1" t="s">
         <v>1488</v>
@@ -20095,7 +20171,7 @@
         <v>344</v>
       </c>
       <c r="G241" s="1" t="s">
-        <v>2514</v>
+        <v>2616</v>
       </c>
       <c r="H241" s="1" t="s">
         <v>1493</v>
@@ -20142,7 +20218,7 @@
         <v>344</v>
       </c>
       <c r="G242" s="1" t="s">
-        <v>2514</v>
+        <v>2616</v>
       </c>
       <c r="H242" s="1" t="s">
         <v>1498</v>
@@ -20189,7 +20265,7 @@
         <v>344</v>
       </c>
       <c r="G243" s="1" t="s">
-        <v>2514</v>
+        <v>2616</v>
       </c>
       <c r="H243" s="1" t="s">
         <v>1503</v>
@@ -20236,7 +20312,7 @@
         <v>344</v>
       </c>
       <c r="G244" s="1" t="s">
-        <v>2514</v>
+        <v>2616</v>
       </c>
       <c r="H244" s="1" t="s">
         <v>48</v>
@@ -20283,7 +20359,7 @@
         <v>1372</v>
       </c>
       <c r="G245" s="1" t="s">
-        <v>2514</v>
+        <v>2617</v>
       </c>
       <c r="H245" s="1" t="s">
         <v>6</v>
@@ -20330,7 +20406,7 @@
         <v>1372</v>
       </c>
       <c r="G246" s="1" t="s">
-        <v>2514</v>
+        <v>2616</v>
       </c>
       <c r="H246" s="1" t="s">
         <v>1515</v>
@@ -20377,7 +20453,7 @@
         <v>1372</v>
       </c>
       <c r="G247" s="1" t="s">
-        <v>2514</v>
+        <v>2616</v>
       </c>
       <c r="H247" s="1" t="s">
         <v>1515</v>
@@ -20424,7 +20500,7 @@
         <v>321</v>
       </c>
       <c r="G248" s="1" t="s">
-        <v>2514</v>
+        <v>2599</v>
       </c>
       <c r="H248" s="1" t="s">
         <v>321</v>
@@ -20459,7 +20535,7 @@
         <v>321</v>
       </c>
       <c r="G249" s="1" t="s">
-        <v>2514</v>
+        <v>2616</v>
       </c>
       <c r="H249" s="1" t="s">
         <v>321</v>
@@ -20494,7 +20570,7 @@
         <v>1531</v>
       </c>
       <c r="G250" s="1" t="s">
-        <v>2514</v>
+        <v>2618</v>
       </c>
       <c r="H250" s="1" t="s">
         <v>1532</v>
@@ -20541,7 +20617,7 @@
         <v>344</v>
       </c>
       <c r="G251" s="1" t="s">
-        <v>2514</v>
+        <v>2616</v>
       </c>
       <c r="H251" s="1" t="s">
         <v>1537</v>
@@ -20588,7 +20664,7 @@
         <v>218</v>
       </c>
       <c r="G252" s="1" t="s">
-        <v>2514</v>
+        <v>44</v>
       </c>
       <c r="H252" s="1" t="s">
         <v>1542</v>
@@ -20635,7 +20711,7 @@
         <v>344</v>
       </c>
       <c r="G253" s="1" t="s">
-        <v>2514</v>
+        <v>2616</v>
       </c>
       <c r="H253" s="1" t="s">
         <v>1547</v>
@@ -20682,7 +20758,7 @@
         <v>344</v>
       </c>
       <c r="G254" s="1" t="s">
-        <v>2514</v>
+        <v>2616</v>
       </c>
       <c r="H254" s="1" t="s">
         <v>1478</v>
@@ -20729,7 +20805,7 @@
         <v>344</v>
       </c>
       <c r="G255" s="1" t="s">
-        <v>2514</v>
+        <v>2616</v>
       </c>
       <c r="H255" s="1" t="s">
         <v>1542</v>
@@ -20776,7 +20852,7 @@
         <v>344</v>
       </c>
       <c r="G256" s="1" t="s">
-        <v>2514</v>
+        <v>2616</v>
       </c>
       <c r="H256" s="1" t="s">
         <v>1488</v>
@@ -20823,7 +20899,7 @@
         <v>1564</v>
       </c>
       <c r="G257" s="1" t="s">
-        <v>2514</v>
+        <v>2619</v>
       </c>
       <c r="H257" s="1" t="s">
         <v>6</v>
@@ -20870,7 +20946,7 @@
         <v>1569</v>
       </c>
       <c r="G258" s="1" t="s">
-        <v>2514</v>
+        <v>2599</v>
       </c>
       <c r="H258" s="1" t="s">
         <v>1570</v>
@@ -20917,7 +20993,7 @@
         <v>1569</v>
       </c>
       <c r="G259" s="1" t="s">
-        <v>2514</v>
+        <v>2599</v>
       </c>
       <c r="H259" s="1" t="s">
         <v>1575</v>
@@ -20964,7 +21040,7 @@
         <v>344</v>
       </c>
       <c r="G260" s="1" t="s">
-        <v>2514</v>
+        <v>2616</v>
       </c>
       <c r="H260" s="1" t="s">
         <v>48</v>
@@ -21011,7 +21087,7 @@
         <v>344</v>
       </c>
       <c r="G261" s="1" t="s">
-        <v>2514</v>
+        <v>2616</v>
       </c>
       <c r="H261" s="1" t="s">
         <v>1584</v>
@@ -21058,7 +21134,7 @@
         <v>1378</v>
       </c>
       <c r="G262" s="1" t="s">
-        <v>2514</v>
+        <v>45</v>
       </c>
       <c r="H262" s="1" t="s">
         <v>1589</v>
@@ -21105,7 +21181,7 @@
         <v>344</v>
       </c>
       <c r="G263" s="1" t="s">
-        <v>2514</v>
+        <v>2616</v>
       </c>
       <c r="H263" s="1" t="s">
         <v>1594</v>
@@ -21152,7 +21228,7 @@
         <v>1599</v>
       </c>
       <c r="G264" s="1" t="s">
-        <v>2514</v>
+        <v>2599</v>
       </c>
       <c r="H264" s="1" t="s">
         <v>1600</v>
@@ -21199,7 +21275,7 @@
         <v>344</v>
       </c>
       <c r="G265" s="1" t="s">
-        <v>2514</v>
+        <v>2616</v>
       </c>
       <c r="H265" s="1" t="s">
         <v>6</v>
@@ -21246,7 +21322,7 @@
         <v>1372</v>
       </c>
       <c r="G266" s="1" t="s">
-        <v>2514</v>
+        <v>2616</v>
       </c>
       <c r="H266" s="1" t="s">
         <v>6</v>
@@ -21293,7 +21369,7 @@
         <v>1611</v>
       </c>
       <c r="G267" s="1" t="s">
-        <v>2514</v>
+        <v>2617</v>
       </c>
       <c r="H267" s="1" t="s">
         <v>6</v>
@@ -21340,7 +21416,7 @@
         <v>344</v>
       </c>
       <c r="G268" s="1" t="s">
-        <v>2514</v>
+        <v>2616</v>
       </c>
       <c r="H268" s="1" t="s">
         <v>1616</v>
@@ -21387,7 +21463,7 @@
         <v>1622</v>
       </c>
       <c r="G269" s="1" t="s">
-        <v>2514</v>
+        <v>2617</v>
       </c>
       <c r="H269" s="1" t="s">
         <v>1616</v>
@@ -21434,7 +21510,7 @@
         <v>1628</v>
       </c>
       <c r="G270" s="1" t="s">
-        <v>2514</v>
+        <v>2617</v>
       </c>
       <c r="H270" s="1" t="s">
         <v>1629</v>
@@ -21481,7 +21557,7 @@
         <v>1628</v>
       </c>
       <c r="G271" s="1" t="s">
-        <v>2514</v>
+        <v>2617</v>
       </c>
       <c r="H271" s="1" t="s">
         <v>1635</v>
@@ -21528,7 +21604,7 @@
         <v>1628</v>
       </c>
       <c r="G272" s="1" t="s">
-        <v>2514</v>
+        <v>2617</v>
       </c>
       <c r="H272" s="1" t="s">
         <v>1641</v>
@@ -21575,7 +21651,7 @@
         <v>1628</v>
       </c>
       <c r="G273" s="1" t="s">
-        <v>2514</v>
+        <v>2617</v>
       </c>
       <c r="H273" s="1" t="s">
         <v>1647</v>
@@ -21622,7 +21698,7 @@
         <v>1652</v>
       </c>
       <c r="G274" s="1" t="s">
-        <v>2514</v>
+        <v>2618</v>
       </c>
       <c r="H274" s="1" t="s">
         <v>1653</v>
@@ -21669,7 +21745,7 @@
         <v>1652</v>
       </c>
       <c r="G275" s="1" t="s">
-        <v>2514</v>
+        <v>2617</v>
       </c>
       <c r="H275" s="1" t="s">
         <v>1658</v>
@@ -21716,7 +21792,7 @@
         <v>1652</v>
       </c>
       <c r="G276" s="1" t="s">
-        <v>2514</v>
+        <v>2617</v>
       </c>
       <c r="H276" s="1" t="s">
         <v>1663</v>
@@ -21763,7 +21839,7 @@
         <v>1669</v>
       </c>
       <c r="G277" s="1" t="s">
-        <v>2514</v>
+        <v>2617</v>
       </c>
       <c r="H277" s="1" t="s">
         <v>1670</v>
@@ -21810,7 +21886,7 @@
         <v>1652</v>
       </c>
       <c r="G278" s="1" t="s">
-        <v>2514</v>
+        <v>2617</v>
       </c>
       <c r="H278" s="1" t="s">
         <v>1675</v>
@@ -21857,7 +21933,7 @@
         <v>1680</v>
       </c>
       <c r="G279" s="1" t="s">
-        <v>2514</v>
+        <v>2620</v>
       </c>
       <c r="H279" s="1" t="s">
         <v>1681</v>
@@ -21904,7 +21980,7 @@
         <v>1652</v>
       </c>
       <c r="G280" s="1" t="s">
-        <v>2514</v>
+        <v>2621</v>
       </c>
       <c r="H280" s="1" t="s">
         <v>1686</v>
@@ -21951,7 +22027,7 @@
         <v>344</v>
       </c>
       <c r="G281" s="1" t="s">
-        <v>2514</v>
+        <v>2616</v>
       </c>
       <c r="H281" s="1" t="s">
         <v>1690</v>
@@ -21998,7 +22074,7 @@
         <v>1652</v>
       </c>
       <c r="G282" s="1" t="s">
-        <v>2514</v>
+        <v>2617</v>
       </c>
       <c r="H282" s="1" t="s">
         <v>1695</v>
@@ -22045,7 +22121,7 @@
         <v>1652</v>
       </c>
       <c r="G283" s="1" t="s">
-        <v>2514</v>
+        <v>2618</v>
       </c>
       <c r="H283" s="1" t="s">
         <v>1700</v>
@@ -22092,7 +22168,7 @@
         <v>1652</v>
       </c>
       <c r="G284" s="1" t="s">
-        <v>2514</v>
+        <v>2617</v>
       </c>
       <c r="H284" s="1" t="s">
         <v>1705</v>
@@ -22139,7 +22215,7 @@
         <v>1652</v>
       </c>
       <c r="G285" s="1" t="s">
-        <v>2514</v>
+        <v>2598</v>
       </c>
       <c r="H285" s="1" t="s">
         <v>1710</v>
@@ -22186,7 +22262,7 @@
         <v>1652</v>
       </c>
       <c r="G286" s="1" t="s">
-        <v>2514</v>
+        <v>2622</v>
       </c>
       <c r="H286" s="1" t="s">
         <v>1714</v>
@@ -22233,7 +22309,7 @@
         <v>1652</v>
       </c>
       <c r="G287" s="1" t="s">
-        <v>2514</v>
+        <v>2617</v>
       </c>
       <c r="H287" s="1" t="s">
         <v>1719</v>
@@ -22280,7 +22356,7 @@
         <v>1680</v>
       </c>
       <c r="G288" s="1" t="s">
-        <v>2514</v>
+        <v>2623</v>
       </c>
       <c r="H288" s="1" t="s">
         <v>1670</v>
@@ -22327,7 +22403,7 @@
         <v>1652</v>
       </c>
       <c r="G289" s="1" t="s">
-        <v>2514</v>
+        <v>2624</v>
       </c>
       <c r="H289" s="1" t="s">
         <v>1726</v>
@@ -22374,7 +22450,7 @@
         <v>514</v>
       </c>
       <c r="G290" s="1" t="s">
-        <v>2514</v>
+        <v>2625</v>
       </c>
       <c r="H290" s="1" t="s">
         <v>1616</v>
@@ -22421,7 +22497,7 @@
         <v>1735</v>
       </c>
       <c r="G291" s="1" t="s">
-        <v>2514</v>
+        <v>43</v>
       </c>
       <c r="H291" s="1" t="s">
         <v>1736</v>
@@ -22468,7 +22544,7 @@
         <v>344</v>
       </c>
       <c r="G292" s="1" t="s">
-        <v>2514</v>
+        <v>2616</v>
       </c>
       <c r="H292" s="1" t="s">
         <v>48</v>
@@ -22515,7 +22591,7 @@
         <v>1744</v>
       </c>
       <c r="G293" s="1" t="s">
-        <v>2514</v>
+        <v>42</v>
       </c>
       <c r="H293" s="1" t="s">
         <v>1745</v>
@@ -22562,7 +22638,7 @@
         <v>1744</v>
       </c>
       <c r="G294" s="1" t="s">
-        <v>2514</v>
+        <v>42</v>
       </c>
       <c r="H294" s="1" t="s">
         <v>1745</v>
@@ -22609,7 +22685,7 @@
         <v>344</v>
       </c>
       <c r="G295" s="1" t="s">
-        <v>2514</v>
+        <v>2616</v>
       </c>
       <c r="H295" s="1" t="s">
         <v>1752</v>
@@ -22656,7 +22732,7 @@
         <v>344</v>
       </c>
       <c r="G296" s="1" t="s">
-        <v>2514</v>
+        <v>2616</v>
       </c>
       <c r="H296" s="1" t="s">
         <v>1752</v>
@@ -22703,7 +22779,7 @@
         <v>1760</v>
       </c>
       <c r="G297" s="1" t="s">
-        <v>2514</v>
+        <v>2626</v>
       </c>
       <c r="H297" s="1" t="s">
         <v>1761</v>
@@ -22750,7 +22826,7 @@
         <v>1765</v>
       </c>
       <c r="G298" s="1" t="s">
-        <v>2514</v>
+        <v>2597</v>
       </c>
       <c r="H298" s="1" t="s">
         <v>1766</v>
@@ -22797,7 +22873,7 @@
         <v>344</v>
       </c>
       <c r="G299" s="1" t="s">
-        <v>2514</v>
+        <v>2616</v>
       </c>
       <c r="H299" s="1" t="s">
         <v>1770</v>
@@ -22844,7 +22920,7 @@
         <v>344</v>
       </c>
       <c r="G300" s="1" t="s">
-        <v>2514</v>
+        <v>2616</v>
       </c>
       <c r="H300" s="1" t="s">
         <v>6</v>
@@ -22891,7 +22967,7 @@
         <v>344</v>
       </c>
       <c r="G301" s="1" t="s">
-        <v>2514</v>
+        <v>2616</v>
       </c>
       <c r="H301" s="1" t="s">
         <v>402</v>
@@ -22938,7 +23014,7 @@
         <v>344</v>
       </c>
       <c r="G302" s="1" t="s">
-        <v>2514</v>
+        <v>2616</v>
       </c>
       <c r="H302" s="1" t="s">
         <v>402</v>
@@ -22985,7 +23061,7 @@
         <v>1786</v>
       </c>
       <c r="G303" s="1" t="s">
-        <v>2514</v>
+        <v>42</v>
       </c>
       <c r="H303" s="1" t="s">
         <v>1787</v>
@@ -23032,7 +23108,7 @@
         <v>344</v>
       </c>
       <c r="G304" s="1" t="s">
-        <v>2514</v>
+        <v>2616</v>
       </c>
       <c r="H304" s="1" t="s">
         <v>1791</v>
@@ -23079,7 +23155,7 @@
         <v>344</v>
       </c>
       <c r="G305" s="1" t="s">
-        <v>2514</v>
+        <v>2616</v>
       </c>
       <c r="H305" s="1" t="s">
         <v>1796</v>
@@ -23126,7 +23202,7 @@
         <v>344</v>
       </c>
       <c r="G306" s="1" t="s">
-        <v>2514</v>
+        <v>2616</v>
       </c>
       <c r="H306" s="1" t="s">
         <v>1801</v>
@@ -23173,7 +23249,7 @@
         <v>344</v>
       </c>
       <c r="G307" s="1" t="s">
-        <v>2514</v>
+        <v>2616</v>
       </c>
       <c r="H307" s="1" t="s">
         <v>1806</v>
@@ -23220,7 +23296,7 @@
         <v>344</v>
       </c>
       <c r="G308" s="1" t="s">
-        <v>2514</v>
+        <v>2616</v>
       </c>
       <c r="H308" s="1" t="s">
         <v>1801</v>
@@ -23267,7 +23343,7 @@
         <v>344</v>
       </c>
       <c r="G309" s="1" t="s">
-        <v>2514</v>
+        <v>2616</v>
       </c>
       <c r="H309" s="1" t="s">
         <v>48</v>
@@ -23314,7 +23390,7 @@
         <v>344</v>
       </c>
       <c r="G310" s="1" t="s">
-        <v>2514</v>
+        <v>2616</v>
       </c>
       <c r="H310" s="1" t="s">
         <v>1820</v>
@@ -23361,7 +23437,7 @@
         <v>1825</v>
       </c>
       <c r="G311" s="1" t="s">
-        <v>2514</v>
+        <v>2627</v>
       </c>
       <c r="H311" s="1" t="s">
         <v>6</v>
@@ -23408,7 +23484,7 @@
         <v>344</v>
       </c>
       <c r="G312" s="1" t="s">
-        <v>2514</v>
+        <v>2616</v>
       </c>
       <c r="H312" s="1" t="s">
         <v>1830</v>
@@ -23455,7 +23531,7 @@
         <v>344</v>
       </c>
       <c r="G313" s="1" t="s">
-        <v>2514</v>
+        <v>2616</v>
       </c>
       <c r="H313" s="1" t="s">
         <v>1835</v>
@@ -23502,7 +23578,7 @@
         <v>1840</v>
       </c>
       <c r="G314" s="1" t="s">
-        <v>2514</v>
+        <v>42</v>
       </c>
       <c r="H314" s="1" t="s">
         <v>48</v>
@@ -23549,7 +23625,7 @@
         <v>344</v>
       </c>
       <c r="G315" s="1" t="s">
-        <v>2514</v>
+        <v>2616</v>
       </c>
       <c r="H315" s="1" t="s">
         <v>1844</v>
@@ -23596,7 +23672,7 @@
         <v>344</v>
       </c>
       <c r="G316" s="1" t="s">
-        <v>2514</v>
+        <v>2616</v>
       </c>
       <c r="H316" s="1" t="s">
         <v>1009</v>
@@ -23643,7 +23719,7 @@
         <v>514</v>
       </c>
       <c r="G317" s="1" t="s">
-        <v>2514</v>
+        <v>2630</v>
       </c>
       <c r="H317" s="1" t="s">
         <v>6</v>
@@ -23690,7 +23766,7 @@
         <v>344</v>
       </c>
       <c r="G318" s="1" t="s">
-        <v>2514</v>
+        <v>2616</v>
       </c>
       <c r="H318" s="1" t="s">
         <v>402</v>
@@ -23737,7 +23813,7 @@
         <v>344</v>
       </c>
       <c r="G319" s="1" t="s">
-        <v>2514</v>
+        <v>2616</v>
       </c>
       <c r="H319" s="1" t="s">
         <v>402</v>
@@ -23784,7 +23860,7 @@
         <v>344</v>
       </c>
       <c r="G320" s="1" t="s">
-        <v>2514</v>
+        <v>2616</v>
       </c>
       <c r="H320" s="1" t="s">
         <v>402</v>
@@ -23831,7 +23907,7 @@
         <v>344</v>
       </c>
       <c r="G321" s="1" t="s">
-        <v>2514</v>
+        <v>2616</v>
       </c>
       <c r="H321" s="1" t="s">
         <v>1864</v>
@@ -28954,7 +29030,7 @@
         <v>377</v>
       </c>
       <c r="G430" s="1" t="s">
-        <v>2514</v>
+        <v>2600</v>
       </c>
       <c r="H430" s="1" t="s">
         <v>2291</v>
@@ -29001,7 +29077,7 @@
         <v>2296</v>
       </c>
       <c r="G431" s="1" t="s">
-        <v>2514</v>
+        <v>2596</v>
       </c>
       <c r="H431" s="1" t="s">
         <v>2297</v>
@@ -29048,7 +29124,7 @@
         <v>425</v>
       </c>
       <c r="G432" s="1" t="s">
-        <v>2514</v>
+        <v>2600</v>
       </c>
       <c r="H432" s="1" t="s">
         <v>6</v>
@@ -29095,7 +29171,7 @@
         <v>1077</v>
       </c>
       <c r="G433" s="1" t="s">
-        <v>2514</v>
+        <v>2628</v>
       </c>
       <c r="H433" s="1" t="s">
         <v>2305</v>
@@ -29142,7 +29218,7 @@
         <v>268</v>
       </c>
       <c r="G434" s="1" t="s">
-        <v>2514</v>
+        <v>46</v>
       </c>
       <c r="H434" s="1" t="s">
         <v>2309</v>
@@ -29377,7 +29453,7 @@
         <v>514</v>
       </c>
       <c r="G439" s="1" t="s">
-        <v>2514</v>
+        <v>2639</v>
       </c>
       <c r="H439" s="1" t="s">
         <v>296</v>
@@ -29464,7 +29540,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B785887B-576B-4D81-AE70-D107EA8277F5}">
-  <dimension ref="A1:R134"/>
+  <dimension ref="A1:R137"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="3" width="9.81640625" customWidth="1"/>
@@ -36579,6 +36655,165 @@
       </c>
       <c r="Q134" t="s">
         <v>181</v>
+      </c>
+    </row>
+    <row r="135" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A135" t="s">
+        <v>2629</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>1849</v>
+      </c>
+      <c r="C135" t="s">
+        <v>44</v>
+      </c>
+      <c r="D135" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E135" t="s">
+        <v>2633</v>
+      </c>
+      <c r="F135" t="s">
+        <v>2636</v>
+      </c>
+      <c r="G135" s="4">
+        <v>3</v>
+      </c>
+      <c r="H135" s="7" t="s">
+        <v>2637</v>
+      </c>
+      <c r="I135" t="s">
+        <v>2630</v>
+      </c>
+      <c r="J135" t="s">
+        <v>6</v>
+      </c>
+      <c r="K135" t="s">
+        <v>2514</v>
+      </c>
+      <c r="L135" s="4" t="s">
+        <v>2462</v>
+      </c>
+      <c r="M135" t="s">
+        <v>2434</v>
+      </c>
+      <c r="N135" t="s">
+        <v>2452</v>
+      </c>
+      <c r="O135" t="s">
+        <v>2434</v>
+      </c>
+      <c r="P135" t="s">
+        <v>2434</v>
+      </c>
+      <c r="Q135" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="136" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A136" t="s">
+        <v>2631</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>1849</v>
+      </c>
+      <c r="C136" t="s">
+        <v>43</v>
+      </c>
+      <c r="D136" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E136" t="s">
+        <v>2633</v>
+      </c>
+      <c r="F136" t="s">
+        <v>2634</v>
+      </c>
+      <c r="G136" s="4">
+        <v>3</v>
+      </c>
+      <c r="H136" s="7" t="s">
+        <v>2635</v>
+      </c>
+      <c r="I136" t="s">
+        <v>2630</v>
+      </c>
+      <c r="J136" t="s">
+        <v>6</v>
+      </c>
+      <c r="K136" t="s">
+        <v>2514</v>
+      </c>
+      <c r="L136" s="4" t="s">
+        <v>2462</v>
+      </c>
+      <c r="M136" t="s">
+        <v>2434</v>
+      </c>
+      <c r="N136" t="s">
+        <v>2452</v>
+      </c>
+      <c r="O136" t="s">
+        <v>2434</v>
+      </c>
+      <c r="P136" t="s">
+        <v>2434</v>
+      </c>
+      <c r="Q136" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="137" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A137" t="s">
+        <v>2632</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>1849</v>
+      </c>
+      <c r="C137" t="s">
+        <v>42</v>
+      </c>
+      <c r="D137" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E137" t="s">
+        <v>2633</v>
+      </c>
+      <c r="F137" t="s">
+        <v>2636</v>
+      </c>
+      <c r="G137" s="4">
+        <v>3</v>
+      </c>
+      <c r="H137" s="7" t="s">
+        <v>2638</v>
+      </c>
+      <c r="I137" t="s">
+        <v>2630</v>
+      </c>
+      <c r="J137" t="s">
+        <v>6</v>
+      </c>
+      <c r="K137" t="s">
+        <v>2514</v>
+      </c>
+      <c r="L137" s="4" t="s">
+        <v>2462</v>
+      </c>
+      <c r="M137" t="s">
+        <v>2434</v>
+      </c>
+      <c r="N137" t="s">
+        <v>2452</v>
+      </c>
+      <c r="O137" t="s">
+        <v>2434</v>
+      </c>
+      <c r="P137" t="s">
+        <v>2434</v>
+      </c>
+      <c r="Q137" t="s">
+        <v>2557</v>
       </c>
     </row>
   </sheetData>
